--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Deviations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Blocked - Not Built" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Blocked - Environment" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Pending" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pending (Re-VIU)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Known Deviations &amp; Blocked" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -459,7 +459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fees &amp; Discounts V1 — FRESH full VIU pass, 2026-07-10 (all 182 cases re-adjudicated)</t>
+          <t>Fees &amp; Discounts V1 — FRESH full VIU pass, 2026-07-10 (all 183 cases; V1_2 spec overlay applied 2026-07-13)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -550,15 +550,15 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Pending (Re-VIU)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Not yet verifiable (blocked by the line-create environment bug)</t>
+          <t>Needs a live re-VIU — includes the V1_2 (2026-07-13) re-VIU-pending set (history-gating flip S13-R10 + new §5-R15 case) plus the pre-existing line-create env-bug case</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
     </row>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2492,32 +2492,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-003</t>
+          <t>FD-INLINE-001</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>C28562</t>
+          <t>C28454</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify an adjustment entry leaves the saved-state icon empty and the Line column shows "−"</t>
+          <t>Verify a labor-line adjustment shows inline under its line with ↳ arrow, name, signed rate badge and grey amount</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2527,39 +2527,39 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch</t>
+          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo})</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-005</t>
+          <t>FD-INLINE-002</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>C28564</t>
+          <t>C28455</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify F&amp;D history stays visible when the F&amp;D UI is hidden by See Financial Data being off</t>
+          <t>Verify a part-line adjustment shows inline under its part with ↳ arrow, name, signed rate badge and grey amount</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2569,39 +2569,39 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD</t>
+          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-006</t>
+          <t>FD-INLINE-004</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>C28565</t>
+          <t>C28457</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>History log — permission</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history entries are gated by the View History Logs permission</t>
+          <t>Verify the per-line Total column shows the line's gross total plus its own adjustment amounts (display only)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2611,39 +2611,39 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model</t>
+          <t>batch evidence stands (Total column incl own adjustments); not re-driven</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-008</t>
+          <t>FD-INLINE-005</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C28567</t>
+          <t>C28458</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>History log — edit entry</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify each inline adjustment row has a hover 3-dot Edit/Delete menu when the WO is open with the matching Create and Edit permission</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2653,34 +2653,34 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>work_order.adjustment.updated entry written on edit (set rate carried)</t>
+          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-001</t>
+          <t>FD-LABOR-002</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>C28454</t>
+          <t>C28440</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment shows inline under its line with ↳ arrow, name, signed rate badge and grey amount</t>
+          <t>Verify a labor-line % of Labor Total fee resolves against the line's gross labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2695,39 +2695,39 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo})</t>
+          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-002</t>
+          <t>FD-LABOR-003</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C28455</t>
+          <t>C28441</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment shows inline under its part with ↳ arrow, name, signed rate badge and grey amount</t>
+          <t>Verify each labor line row exposes its own 3-dot menu on hover</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2737,34 +2737,34 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven)</t>
+          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-004</t>
+          <t>FD-LABOR-004</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C28457</t>
+          <t>C28442</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-line Total column shows the line's gross total plus its own adjustment amounts (display only)</t>
+          <t>Verify a labor-line Flat Amount resolves to the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2779,34 +2779,34 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>batch evidence stands (Total column incl own adjustments); not re-driven</t>
+          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-005</t>
+          <t>FD-LABOR-005</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C28458</t>
+          <t>C28443</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline adjustment row has a hover 3-dot Edit/Delete menu when the WO is open with change permission</t>
+          <t>Verify a labor-line adjustment resolves to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2821,24 +2821,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove')</t>
+          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-002</t>
+          <t>FD-LABOR-006</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>C28440</t>
+          <t>C28444</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line % of Labor Total fee resolves against the line's gross labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify deleting a labor line removes any adjustment pointing to it</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands</t>
+          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-003</t>
+          <t>FD-LABOR-007</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C28441</t>
+          <t>C28445</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row exposes its own 3-dot menu on hover</t>
+          <t>Verify labor-line 'Add fee / discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2905,39 +2905,39 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API</t>
+          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-004</t>
+          <t>FD-PART-002</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C28442</t>
+          <t>C28447</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line Flat Amount resolves to the exact amount with no quantity multiplier</t>
+          <t>Verify a part-line Flat Amount is charged PER ITEM (amount × quantity): $5.00 × qty 3 → −$15.00</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2947,39 +2947,39 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier</t>
+          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00')</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-005</t>
+          <t>FD-PART-003</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C28443</t>
+          <t>C28448</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment resolves to $0.00 when its line is not billable (declined)</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2989,39 +2989,39 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500)</t>
+          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-006</t>
+          <t>FD-PART-004</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>C28444</t>
+          <t>C28449</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any adjustment pointing to it</t>
+          <t>Verify a part-line % of Parts Total resolves against quantity × sell price (gross)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3031,34 +3031,34 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide)</t>
+          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-007</t>
+          <t>FD-PART-006</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C28445</t>
+          <t>C28451</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line 'Add fee / discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3073,24 +3073,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives</t>
+          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-002</t>
+          <t>FD-PART-007</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C28447</t>
+          <t>C28452</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line Flat Amount is charged PER ITEM (amount × quantity): $5.00 × qty 3 → −$15.00</t>
+          <t>Verify deleting a part removes any adjustment pointing to it</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3115,24 +3115,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00')</t>
+          <t>prior delete-cascade (batch-4) stands; not re-seedable today</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-003</t>
+          <t>FD-PART-008</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C28448</t>
+          <t>C28453</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
+          <t>Verify per-item Flat Amount edge: quantity 1 resolves to the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3157,34 +3157,34 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500)</t>
+          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-004</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>C28449</t>
+          <t>C28585</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line % of Parts Total resolves against quantity × sell price (gross)</t>
+          <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3199,39 +3199,39 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08</t>
+          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00')</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-006</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C28451</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3241,39 +3241,39 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock)</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-007</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C28452</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any adjustment pointing to it</t>
+          <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3283,39 +3283,39 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>prior delete-cascade (batch-4) stands; not re-seedable today</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-008</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C28453</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify per-item Flat Amount edge: quantity 1 resolves to the base amount (−$5.00)</t>
+          <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3325,24 +3325,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C28585</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
+          <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3367,24 +3367,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00')</t>
+          <t>templates admin BE-enforced: tech GET/POST 403</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3409,24 +3409,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat)</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
+          <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3451,24 +3451,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed)</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
+          <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3493,34 +3493,34 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency)</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3535,34 +3535,34 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3577,34 +3577,34 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>C28593</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the WO history log requires View History Logs (and stays visible even when F&amp;D UI is hidden)</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3619,39 +3619,39 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3661,34 +3661,34 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON)</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee'</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3703,39 +3703,39 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock)</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3745,39 +3745,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3787,39 +3787,39 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto)</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3829,39 +3829,39 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5)</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3871,39 +3871,39 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee'</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify removing an adjustment uses 'Create and Edit', NOT the 'Delete' permission</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0)</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
+          <t>Verify removing a line-level adjustment via its inline 3-dot menu</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3955,39 +3955,39 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time)</t>
+          <t>line-level remove 204 and gone from the line</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify multiple adjustments on one part each resolve on the part's own base (do not compound) and net correctly</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3997,39 +3997,39 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
+          <t>Verify two whole-WO percentage adjustments resolve against the same net totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4039,39 +4039,39 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4081,34 +4081,34 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify removing an adjustment uses 'Create and Edit', NOT the 'Delete' permission</t>
+          <t>Verify the Stats F&amp;D breakdown Total row equals the signed sum of all resolved amounts, with correct signs</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4123,34 +4123,34 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency)</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level adjustment via its inline 3-dot menu</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the WO has no adjustments</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4165,34 +4165,34 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple adjustments on one part each resolve on the part's own base (do not compound) and net correctly</t>
+          <t>Verify the template list columns and the delete action</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4207,34 +4207,34 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding)</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-WO percentage adjustments resolve against the same net totals and do not change each other's base</t>
+          <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4249,39 +4249,39 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding)</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify the template delete confirm dialog copy and buttons</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4291,34 +4291,34 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats F&amp;D breakdown Total row equals the signed sum of all resolved amounts, with correct signs</t>
+          <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4333,34 +4333,34 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the WO has no adjustments</t>
+          <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4375,39 +4375,39 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the delete action</t>
+          <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4417,39 +4417,39 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts'</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
+          <t>Verify the template save-failure toast</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4459,34 +4459,34 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog copy and buttons</t>
+          <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4501,39 +4501,39 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
+          <t>Verify template Name enforces the 100-character limit</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4543,39 +4543,39 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact)</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
+          <t>Verify a blank or 0 Amount/Percent blocks save with an inline error</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4585,34 +4585,34 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
+          <t>Verify an empty Name blocks save with an inline error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4627,39 +4627,39 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts'</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28602</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure toast</t>
+          <t>Verify a percentage discount &gt; 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4669,39 +4669,39 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced)</t>
+          <t>discount &gt;100% invalid (400), fee uncapped (201)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28603</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
+          <t>Verify negative Amount/Percent values are rejected (values must be &gt; 0)</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4711,39 +4711,39 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance</t>
+          <t>negative amount -&gt; 400</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28605</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify template Name enforces the 100-character limit</t>
+          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4753,39 +4753,39 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400</t>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-WO-002</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28425</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 Amount/Percent blocks save with an inline error</t>
+          <t>Verify adding a whole-WO Flat Amount fee saves and shows the success toast</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit</t>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-WO-003</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28426</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks save with an inline error (Name required, up to 100 characters)</t>
+          <t>Verify the live preview computes and displays a whole-WO percentage discount (8% of $10,715.39 → −$857.23)</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4837,34 +4837,34 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201</t>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-WO-004</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28427</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount &gt; 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify 'Apply from template' auto-fills the dialog fields with the template's values</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4879,34 +4879,34 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201)</t>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-WO-006</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28429</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify negative Amount/Percent values are rejected (values must be &gt; 0)</t>
+          <t>Verify Max Amount (Max cap) caps a percentage adjustment (20% fee on $100 → +$15 with Max $15)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4921,34 +4921,34 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400</t>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-WO-007</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28430</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO</t>
+          <t>Verify the add confirm button label follows the Type (Add Fee vs Add Discount)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -4963,24 +4963,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO</t>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-WO-008</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28431</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-WO Flat Amount fee saves and shows the success toast</t>
+          <t>Verify an empty Name blocks saving a whole-WO adjustment</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5005,24 +5005,24 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly)</t>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-WO-009</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28432</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview computes and displays a whole-WO percentage discount (8% of $10,715.39 → −$857.23)</t>
+          <t>Verify an empty or zero Amount blocks saving a whole-WO adjustment</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5047,24 +5047,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08)</t>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-WO-010</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28433</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply from template' auto-fills the dialog fields with the template's values</t>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5089,24 +5089,24 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003)</t>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-WO-011</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28434</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount (Max cap) caps a percentage adjustment (20% fee on $100 → +$15 with Max $15)</t>
+          <t>Verify whole-WO percentage methods resolve against the correct base (% of Subtotal example)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15</t>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-WO-012</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28435</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify the add confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify 'Add Fee / Discount' is hidden and rejected on an Invoiced or Paid work order</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5173,24 +5173,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven)</t>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-WO-014</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28437</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-WO adjustment</t>
+          <t>Verify the live preview shows the empty-amount prompt before an amount is entered</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5215,24 +5215,24 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards</t>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-WO-015</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28438</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero Amount blocks saving a whole-WO adjustment</t>
+          <t>Verify the preview adjustment row is signed and colored (fee vs discount)</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5256,216 +5256,6 @@
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-010</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>C28433</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-011</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>C28434</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Verify whole-WO percentage methods resolve against the correct base (% of Subtotal example)</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-012</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>C28435</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Verify 'Add Fee / Discount' is hidden and rejected on an Invoiced or Paid work order</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-014</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>C28437</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Verify the live preview shows the empty-amount prompt before an amount is entered</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-015</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>C28438</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Verify the preview adjustment row is signed and colored (fee vs discount)</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked)</t>
         </is>
@@ -5582,11 +5372,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5598,7 +5383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6034,27 +5819,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-001</t>
+          <t>FD-INLINE-003</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28560</t>
+          <t>C28456</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify a line/part with 2+ adjustments shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6069,39 +5854,39 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery)</t>
+          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-002</t>
+          <t>FD-LABOR-001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28561</t>
+          <t>C28439</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify the history detail block shows Name, Type, Amount (set rate), and Applied-to label</t>
+          <t>Verify a labor line's 3-dot menu opens the Add dialog locked to that Labor Line scope</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6111,39 +5896,39 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven</t>
+          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-007</t>
+          <t>FD-PART-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28566</t>
+          <t>C28446</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>History log — Processing Fee</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee with "Full invoice" applied-to and no "updated" entry</t>
+          <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6153,34 +5938,34 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly)</t>
+          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-003</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28456</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify a line/part with 2+ adjustments shows only the first plus a 'Show N more' toggle</t>
+          <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -6195,39 +5980,39 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-001</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28439</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's 3-dot menu opens the Add dialog locked to that Labor Line scope</t>
+          <t>Verify a Processing Fee on a WO can be removed but not edited</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6237,39 +6022,39 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-001</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28446</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
+          <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6279,34 +6064,34 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-002</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6321,34 +6106,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision)</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-008</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28526</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a WO can be removed but not edited</t>
+          <t>Verify removing a whole-WO adjustment shows the 'Remove Fee / Discount' confirm and a success toast</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6363,34 +6148,34 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift)</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-009</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
+          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with Value/% and Amount columns</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -6405,39 +6190,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-STATS-002</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
+          <t>Verify each Stats F&amp;D row shows a scope hyperlink naming its target</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6447,39 +6232,39 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12</t>
+          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-STATS-004</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-WO adjustment shows the 'Remove Fee / Discount' confirm and a success toast</t>
+          <t>Verify the Stats F&amp;D rows are listed in creation order (oldest first)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6489,34 +6274,34 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today</t>
+          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-001</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C28459</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with Value/% and Amount columns</t>
+          <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -6531,39 +6316,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats)</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-002</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C28460</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify each Stats F&amp;D row shows a scope hyperlink naming its target</t>
+          <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6573,34 +6358,34 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001)</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-004</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C28462</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats F&amp;D rows are listed in creation order (oldest first)</t>
+          <t>Verify creating a Discount template shows the "Discount added" toast</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -6615,39 +6400,39 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001)</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
+          <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6657,39 +6442,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target)</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
+          <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6699,39 +6484,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-TMPL-010</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template shows the "Discount added" toast</t>
+          <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6741,34 +6526,34 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
+          <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6783,39 +6568,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
+          <t>Verify the Add button stays DISABLED until Name AND Type AND Calculation type AND Amount &gt; 0 are all set</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6825,39 +6610,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-010</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C28511</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Template admin — scoping</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
+          <t>Verify Max cap edge behavior — 0 or empty = no maximum, and Max Amount shows only for percentage methods</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6867,39 +6652,39 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-WO-001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C28424</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
+          <t>Verify the whole-work-order Add dialog opens from the WO toolbar more (⋯) menu at Whole Work Order scope</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6909,39 +6694,39 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists</t>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-001</t>
+          <t>FD-WO-005</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C28599</t>
+          <t>C28428</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays DISABLED until Name AND Type AND Calculation type AND Amount &gt; 0 are all set</t>
+          <t>Verify the Add button is disabled until Name, Type, Calculation type and Amount&gt;0 are all set</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6951,34 +6736,34 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists</t>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-WO-013</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C28604</t>
+          <t>C28436</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify Max cap edge behavior — 0 or empty = no maximum, and Max Amount shows only for percentage methods</t>
+          <t>Verify whole-WO starting places are hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6992,132 +6777,6 @@
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-001</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>C28424</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Verify the whole-work-order Add dialog opens from the WO toolbar more (⋯) menu at Whole Work Order scope</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-005</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>C28428</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button is disabled until Name, Type, Calculation type and Amount&gt;0 are all set</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-013</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Verify whole-WO starting places are hidden without Work Orders: Create &amp; Edit</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists</t>
         </is>
@@ -7157,9 +6816,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7543,7 +7199,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify Part-Sale part adjustment add/edit/remove requires Part Sales: Create and Edit</t>
+          <t>Verify Part-Sale adjustment add/edit/remove (whole sale or part line) requires Part Sales: Create and Edit + See Financial Data</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7706,12 +7362,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — taxable + legal disclosure</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable control defaults Yes and renders the legal disclosure</t>
+          <t>Verify the Processing Fee Taxable control defaults Yes and shows the §5-R15 jurisdiction note</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7721,7 +7377,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Blocked-NotBuilt (expected rewritten to §5-R15 jurisdiction note per S8-R13; re-check when Story-8 builder ships)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7755,7 +7411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7897,17 +7553,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FD-FLAG-002</t>
+          <t>FD-FLAG-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>C28597</t>
+          <t>C28598</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -7917,7 +7573,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify the WO history log STILL shows fee/discount entries even when the feature flag is OFF</t>
+          <t>Verify with the flag ON, the matching permission is still required to use F&amp;D</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -7932,39 +7588,39 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>as FD-FLAG-001</t>
+          <t>as FD-FLAG-001; the flag-ON half of the AND-gate is fresh-proven (FD-PERM-010)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FD-FLAG-003</t>
+          <t>FD-QB-001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>C28598</t>
+          <t>C28544</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Feature-flag gating</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify with the flag ON, the matching permission is still required to use F&amp;D</t>
+          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee +, discount −)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7974,34 +7630,34 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>as FD-FLAG-001; the flag-ON half of the AND-gate is fresh-proven (FD-PERM-010)</t>
+          <t>QB invoice line internals unobservable (no read API; export of re-invoiced WOs fails on duplicate doc numbers) — needs QB-UI eyeball of a cleanly synced invoice</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-004</t>
+          <t>FD-QB-002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28563</t>
+          <t>C28545</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the feature flag</t>
+          <t>Verify the QuickBooks line description equals the adjustment name and the item is the mapped Fee/Discount item</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -8016,39 +7672,39 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today)</t>
+          <t>as FD-QB-001 — needs QB UI (generic Fee/Discount item + description=name)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-001</t>
+          <t>FD-QB-003</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28544</t>
+          <t>C28546</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync</t>
+          <t>QuickBooks sync — edge</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee +, discount −)</t>
+          <t>Verify a $0.00 resolved adjustment is skipped when sent to QuickBooks</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8058,34 +7714,34 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>QB invoice line internals unobservable (no read API; export of re-invoiced WOs fails on duplicate doc numbers) — needs QB-UI eyeball of a cleanly synced invoice</t>
+          <t>as FD-QB-001 — $0-line skip only visible QB-side</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-002</t>
+          <t>FD-QB-004</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28545</t>
+          <t>C28547</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify the QuickBooks line description equals the adjustment name and the item is the mapped Fee/Discount item</t>
+          <t>Verify adding a fee is blocked when the Fee item is unmapped (exact message)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -8100,39 +7756,39 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-001 — needs QB UI (generic Fee/Discount item + description=name)</t>
+          <t>unmap not achievable today: PUT bookkeeping/settings {settings:{feeItemId:null}} -&gt; 500 (requestId 4bd14847); flat payload -&gt; 400 'settings missing'. Mapping stayed connected+mapped (verified). Guard cycle needs a working unmap (dev/QB-side)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-003</t>
+          <t>FD-QB-005</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28546</t>
+          <t>C28548</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync — edge</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 resolved adjustment is skipped when sent to QuickBooks</t>
+          <t>Verify adding a discount is blocked when the Discount item is unmapped (exact message)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8142,39 +7798,39 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-001 — $0-line skip only visible QB-side</t>
+          <t>as FD-QB-004 (unmap 500)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-004</t>
+          <t>FD-QB-006</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28547</t>
+          <t>C28549</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard</t>
+          <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a fee is blocked when the Fee item is unmapped (exact message)</t>
+          <t>Verify the mapping guard blocks adds on every add surface (WO, labor line, part, part sale, template-apply)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8184,39 +7840,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>unmap not achievable today: PUT bookkeeping/settings {settings:{feeItemId:null}} -&gt; 500 (requestId 4bd14847); flat payload -&gt; 400 'settings missing'. Mapping stayed connected+mapped (verified). Guard cycle needs a working unmap (dev/QB-side)</t>
+          <t>as FD-QB-004 (unmap 500)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-005</t>
+          <t>FD-QB-007</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28548</t>
+          <t>C28550</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard</t>
+          <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a discount is blocked when the Discount item is unmapped (exact message)</t>
+          <t>Verify an auto-apply default cannot be saved while the matching QuickBooks item is unmapped</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8233,27 +7889,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-006</t>
+          <t>FD-QB-008</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28549</t>
+          <t>C28551</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard scope</t>
+          <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify the mapping guard blocks adds on every add surface (WO, labor line, part, part sale, template-apply)</t>
+          <t>Verify creating/editing a non-auto-apply template is always allowed and no block exists when QuickBooks is not connected</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -8268,34 +7924,34 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004 (unmap 500)</t>
+          <t>as FD-QB-004; positive half (template create while MAPPED) works throughout</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-007</t>
+          <t>FD-QB-009</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28550</t>
+          <t>C28552</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard (auto-apply)</t>
+          <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify an auto-apply default cannot be saved while the matching QuickBooks item is unmapped</t>
+          <t>Verify unmapping an in-use item routes affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8310,39 +7966,39 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004 (unmap 500)</t>
+          <t>unexported-items list + retry + mark-done endpoints re-exercised (mark-done 200 on my entries); the unmap-in-flight repro blocked by the unmap 500</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-008</t>
+          <t>FD-QB-010</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28551</t>
+          <t>C28553</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard exceptions</t>
+          <t>QuickBooks — Class</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify creating/editing a non-auto-apply template is always allowed and no block exists when QuickBooks is not connected</t>
+          <t>Verify a single QuickBooks Class applies to every synced line including fee/discount lines</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8352,39 +8008,39 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004; positive half (template create while MAPPED) works throughout</t>
+          <t>Class application only visible QB-side</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-009</t>
+          <t>FD-QB-011</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28552</t>
+          <t>C28554</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — unmap recovery</t>
+          <t>QuickBooks — Class validation</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify unmapping an in-use item routes affected invoices to Unexported Items (recoverable, no data lost)</t>
+          <t>Verify a deleted/deactivated Class aborts the entire invoice sync (no substitution)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8394,39 +8050,39 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>unexported-items list + retry + mark-done endpoints re-exercised (mark-done 200 on my entries); the unmap-in-flight repro blocked by the unmap 500</t>
+          <t>stale-Class abort only reproducible QB-side</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-010</t>
+          <t>FD-QB-013</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28553</t>
+          <t>C28556</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify a single QuickBooks Class applies to every synced line including fee/discount lines</t>
+          <t>Verify discount lines to QuickBooks are capped with largest-remainder whole-cent penny allocation</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8436,39 +8092,39 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Class application only visible QB-side</t>
+          <t>penny-cap allocation of discount LINES only visible on QB invoice lines</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-011</t>
+          <t>FD-QB-015</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28554</t>
+          <t>C28558</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class validation</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify a deleted/deactivated Class aborts the entire invoice sync (no substitution)</t>
+          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit memo</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8478,34 +8134,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>stale-Class abort only reproducible QB-side</t>
+          <t>IN-APP HALF VERIFIED TODAY: invoicing the over-discounted WO recorded a CUSTOMER CREDIT (unpaid-transactions 2-&gt;4; 'current' bucket -11.63 -&gt; -119.73 = +9.14 invoice &amp; -117.24 credit exactly). QB goodwill-memo half unobservable: invoice export fails on the duplicate-doc-number env bug, no credit_memo export fired, no QB read API — needs QB UI on a cleanly synced org</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-013</t>
+          <t>FD-QB-016</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28556</t>
+          <t>C28559</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>QuickBooks sync — tax</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify discount lines to QuickBooks are capped with largest-remainder whole-cent penny allocation</t>
+          <t>Verify a synced line's tax follows the adjustment's taxable setting</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -8520,39 +8176,39 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>penny-cap allocation of discount LINES only visible on QB invoice lines</t>
+          <t>tax code on the QB line unobservable in-app; in-app taxable base shifts re-proven (FD-CALC-011)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-015</t>
+          <t>FD-TMPL-012</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28558</t>
+          <t>C28513</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit memo</t>
+          <t>Verify the template list empty-state message</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8561,90 +8217,6 @@
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>IN-APP HALF VERIFIED TODAY: invoicing the over-discounted WO recorded a CUSTOMER CREDIT (unpaid-transactions 2-&gt;4; 'current' bucket -11.63 -&gt; -119.73 = +9.14 invoice &amp; -117.24 credit exactly). QB goodwill-memo half unobservable: invoice export fails on the duplicate-doc-number env bug, no credit_memo export fired, no QB read API — needs QB UI on a cleanly synced org</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FD-QB-016</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>C28559</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks sync — tax</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Verify a synced line's tax follows the adjustment's taxable setting</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>tax code on the QB line unobservable in-app; in-app taxable base shifts re-proven (FD-CALC-011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-012</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>C28513</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — list</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verify the template list empty-state message</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active)</t>
         </is>
@@ -8670,8 +8242,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8683,7 +8253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8741,48 +8311,516 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>FD-FLAG-002</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>C28597</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Feature-flag gating</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify the WO history log STILL shows fee/discount entries even when the feature flag is OFF</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>C28560</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>History log</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>C28561</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>History log</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify the history detail block shows Name, Type, Amount (set rate), and Applied-to label</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-003</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>C28562</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>History log</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify an adjustment entry leaves the saved-state icon empty and the Line column shows "−"</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-004</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>C28563</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>History log — visibility</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the feature flag</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>C28564</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>History log — visibility</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify F&amp;D history stays visible when the F&amp;D UI is hidden by See Financial Data being off</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-006</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>C28565</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>History log — permission</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-007</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>C28566</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>History log — Processing Fee</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee is logged as a fee with "Full invoice" applied-to and no "updated" entry</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-008</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>C28567</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>History log — edit entry</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>FD-PART-005</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>C28450</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify a part-line adjustment stays attached when the part changes from requested to received</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FD-PERM-009</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>C28593</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify seeing fee/discount entries in the WO history log requires Work Orders: Create and Edit (line history requires Work Order Lines: Create and Edit)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-016</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the §5-R15 taxable jurisdiction note below the Taxable dropdown</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Pending — new case (V1_2 §5-R15 / S2-R26a); not yet checked live</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>NEW 2026-07-13 for V1_2 §5-R15 / S2-R26a. UI string check (advisory) — belongs in a FUNCTIONAL section, NOT an API section (standing rule 4). Assert the exact string verbatim.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -8778,10 +8778,14 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>(pending-create)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
+          <t>C29441</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
@@ -8821,6 +8825,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify editing an adjustment allows Name/Value/Max Amount/Taxable but locks Type, Calculation type, and Scope</t>
+          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200)</t>
+          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit.</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify editing re-resolves the adjustment against current totals, hides the template picker, and uses a 'Save' button</t>
+          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands</t>
+          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01).</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify a save failure keeps the Edit dialog open and shows the returned error</t>
+          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact</t>
+          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a collapsed 'Fees &amp; Discounts (N)' row with the net total in grey</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total</t>
+          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03).</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify expanding the Financial Info 'Fees &amp; Discounts' row lists each adjustment (read-only, creation order)</t>
+          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3</t>
+          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info 'Fees &amp; Discounts' row is hidden with no adjustments and the money section is hidden without See Financial Data</t>
+          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2443,24 +2443,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row</t>
+          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-FIN-004</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>C28468</t>
+          <t>C28467</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar card is hidden with no whole-WO adjustments and has no Add control</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2485,39 +2485,39 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3</t>
+          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-001</t>
+          <t>FD-FIN-005</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>C28454</t>
+          <t>C28468</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment shows inline under its line with ↳ arrow, name, signed rate badge and grey amount</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2527,24 +2527,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo})</t>
+          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-002</t>
+          <t>FD-INLINE-001</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>C28455</t>
+          <t>C28454</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment shows inline under its part with ↳ arrow, name, signed rate badge and grey amount</t>
+          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven)</t>
+          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-004</t>
+          <t>FD-INLINE-002</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>C28457</t>
+          <t>C28455</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-line Total column shows the line's gross total plus its own adjustment amounts (display only)</t>
+          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2611,24 +2611,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>batch evidence stands (Total column incl own adjustments); not re-driven</t>
+          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-005</t>
+          <t>FD-INLINE-004</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C28458</t>
+          <t>C28457</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline adjustment row has a hover 3-dot Edit/Delete menu when the WO is open with the matching Create and Edit permission</t>
+          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2653,39 +2653,39 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove')</t>
+          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-002</t>
+          <t>FD-INLINE-005</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>C28440</t>
+          <t>C28458</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line % of Labor Total fee resolves against the line's gross labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2695,24 +2695,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands</t>
+          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-003</t>
+          <t>FD-LABOR-002</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C28441</t>
+          <t>C28440</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row exposes its own 3-dot menu on hover</t>
+          <t>Verify a labor-line % of Labor Total fee resolves against the line's gross labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2737,24 +2737,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API</t>
+          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-004</t>
+          <t>FD-LABOR-003</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C28442</t>
+          <t>C28441</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line Flat Amount resolves to the exact amount with no quantity multiplier</t>
+          <t>Verify each labor line row exposes its own 3-dot menu on hover</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2779,24 +2779,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier</t>
+          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-005</t>
+          <t>FD-LABOR-004</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C28443</t>
+          <t>C28442</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment resolves to $0.00 when its line is not billable (declined)</t>
+          <t>Verify a labor-line Flat Amount resolves to the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2821,24 +2821,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500)</t>
+          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-006</t>
+          <t>FD-LABOR-005</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>C28444</t>
+          <t>C28443</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any adjustment pointing to it</t>
+          <t>Verify a labor-line adjustment resolves to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide)</t>
+          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-007</t>
+          <t>FD-LABOR-006</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C28445</t>
+          <t>C28444</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line 'Add fee / discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify deleting a labor line removes any adjustment pointing to it</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2905,39 +2905,39 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives</t>
+          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-002</t>
+          <t>FD-LABOR-007</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C28447</t>
+          <t>C28445</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line Flat Amount is charged PER ITEM (amount × quantity): $5.00 × qty 3 → −$15.00</t>
+          <t>Verify labor-line 'Add fee / discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2947,24 +2947,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00')</t>
+          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-003</t>
+          <t>FD-PART-002</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C28448</t>
+          <t>C28447</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
+          <t>Verify a part-line Flat Amount is charged PER ITEM (amount × quantity): $5.00 × qty 3 → −$15.00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2989,24 +2989,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500)</t>
+          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00')</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-004</t>
+          <t>FD-PART-003</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>C28449</t>
+          <t>C28448</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line % of Parts Total resolves against quantity × sell price (gross)</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3031,24 +3031,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08</t>
+          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-006</t>
+          <t>FD-PART-004</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C28451</t>
+          <t>C28449</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify a part-line % of Parts Total resolves against quantity × sell price (gross)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3073,24 +3073,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock)</t>
+          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-007</t>
+          <t>FD-PART-006</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C28452</t>
+          <t>C28451</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any adjustment pointing to it</t>
+          <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3115,24 +3115,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>prior delete-cascade (batch-4) stands; not re-seedable today</t>
+          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-008</t>
+          <t>FD-PART-007</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C28453</t>
+          <t>C28452</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify per-item Flat Amount edge: quantity 1 resolves to the base amount (−$5.00)</t>
+          <t>Verify deleting a part removes any adjustment pointing to it</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3157,39 +3157,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4</t>
+          <t>prior delete-cascade (batch-4) stands; not re-seedable today</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-PART-008</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>C28585</t>
+          <t>C28453</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
+          <t>Verify per-item Flat Amount edge: quantity 1 resolves to the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3199,24 +3199,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00')</t>
+          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28585</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat)</t>
+          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00')</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
+          <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3283,24 +3283,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed)</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
+          <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3325,24 +3325,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency)</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
+          <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3367,24 +3367,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3409,24 +3409,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403</t>
+          <t>templates admin BE-enforced: tech GET/POST 403</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3451,24 +3451,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON)</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
+          <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3493,39 +3493,39 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock)</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3535,34 +3535,34 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3577,39 +3577,39 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto)</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3619,34 +3619,34 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5)</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3661,34 +3661,34 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee'</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3703,34 +3703,34 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0)</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee'</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3745,39 +3745,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time)</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3787,34 +3787,34 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
+          <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3829,39 +3829,39 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
+          <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3871,34 +3871,34 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify removing an adjustment uses 'Create and Edit', NOT the 'Delete' permission</t>
+          <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3913,24 +3913,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency)</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level adjustment via its inline 3-dot menu</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3955,34 +3955,34 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple adjustments on one part each resolve on the part's own base (do not compound) and net correctly</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3997,39 +3997,39 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding)</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-WO percentage adjustments resolve against the same net totals and do not change each other's base</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4039,24 +4039,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding)</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify multiple adjustments on one part each resolve on the part's own base (do not compound) and net correctly</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4081,34 +4081,34 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats F&amp;D breakdown Total row equals the signed sum of all resolved amounts, with correct signs</t>
+          <t>Verify two whole-WO percentage adjustments resolve against the same net totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4123,34 +4123,34 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the WO has no adjustments</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4165,34 +4165,34 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the delete action</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4207,39 +4207,39 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4249,34 +4249,34 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog copy and buttons</t>
+          <t>Verify the template list columns and the delete action</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4291,34 +4291,34 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
+          <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4333,39 +4333,39 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact)</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
+          <t>Verify the template delete confirm dialog copy and buttons</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4375,39 +4375,39 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
+          <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4417,39 +4417,39 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts'</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure toast</t>
+          <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4459,39 +4459,39 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced)</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
+          <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4501,34 +4501,34 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts'</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify template Name enforces the 100-character limit</t>
+          <t>Verify the template save-failure toast</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4543,34 +4543,34 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 Amount/Percent blocks save with an inline error</t>
+          <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4585,39 +4585,39 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks save with an inline error (Name required, up to 100 characters)</t>
+          <t>Verify template Name enforces the 100-character limit</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -4627,24 +4627,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount &gt; 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4669,24 +4669,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201)</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify negative Amount/Percent values are rejected (values must be &gt; 0)</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4711,24 +4711,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28602</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4753,39 +4753,39 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO</t>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28603</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-WO Flat Amount fee saves and shows the success toast</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly)</t>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28605</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview computes and displays a whole-WO percentage discount (8% of $10,715.39 → −$857.23)</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4837,24 +4837,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08)</t>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-WO-001</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28424</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply from template' auto-fills the dialog fields with the template's values</t>
+          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4879,24 +4879,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003)</t>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-WO-002</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28425</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount (Max cap) caps a percentage adjustment (20% fee on $100 → +$15 with Max $15)</t>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4921,24 +4921,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15</t>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-WO-003</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28426</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify the add confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4963,24 +4963,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven)</t>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-WO-004</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28427</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-WO adjustment</t>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5005,24 +5005,24 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards</t>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-WO-006</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28429</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero Amount blocks saving a whole-WO adjustment</t>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5047,24 +5047,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit</t>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-WO-007</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C28430</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5089,24 +5089,24 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201</t>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-WO-008</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28431</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify whole-WO percentage methods resolve against the correct base (% of Subtotal example)</t>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total)</t>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-WO-009</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28432</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Add Fee / Discount' is hidden and rejected on an Invoiced or Paid work order</t>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5173,24 +5173,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409</t>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-WO-010</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28433</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5215,49 +5215,175 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog</t>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>FD-WO-011</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>C28434</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-012</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>C28435</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-014</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>C28437</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-015</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>C28438</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Verify the preview adjustment row is signed and colored (fee vs discount)</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked)</t>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass.</t>
         </is>
       </c>
     </row>
@@ -5372,6 +5498,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5383,7 +5512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5777,27 +5906,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-INLINE-003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28467</t>
+          <t>C28456</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'Work Order Fee / Discount' card lists whole-WO adjustments with name, signed rate badge, grey amount and hover Edit/Delete</t>
+          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5812,39 +5941,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update)</t>
+          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-003</t>
+          <t>FD-LABOR-001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28456</t>
+          <t>C28439</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify a line/part with 2+ adjustments shows only the first plus a 'Show N more' toggle</t>
+          <t>Verify a labor line's 3-dot menu opens the Add dialog locked to that Labor Line scope</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5854,34 +5983,34 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists</t>
+          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-001</t>
+          <t>FD-PART-001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28439</t>
+          <t>C28446</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's 3-dot menu opens the Add dialog locked to that Labor Line scope</t>
+          <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5896,39 +6025,39 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today</t>
+          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-001</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28446</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
+          <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5938,34 +6067,34 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-002</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify a Processing Fee on a WO can be removed but not edited</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5980,34 +6109,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision)</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-008</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28526</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a WO can be removed but not edited</t>
+          <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -6022,34 +6151,34 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift)</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-009</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
+          <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -6064,34 +6193,34 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
+          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6106,39 +6235,39 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-STATS-002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-WO adjustment shows the 'Remove Fee / Discount' confirm and a success toast</t>
+          <t>Verify each Stats fee/discount row names its target</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6148,24 +6277,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today</t>
+          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-001</t>
+          <t>FD-STATS-004</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28459</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -6175,12 +6304,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with Value/% and Amount columns</t>
+          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6190,39 +6319,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats)</t>
+          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-002</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C28460</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify each Stats F&amp;D row shows a scope hyperlink naming its target</t>
+          <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6232,39 +6361,39 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001)</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-004</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C28462</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats F&amp;D rows are listed in creation order (oldest first)</t>
+          <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6274,39 +6403,39 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001)</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
+          <t>Verify creating a Discount template shows the "Discount added" toast</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6316,39 +6445,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target)</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
+          <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6358,34 +6487,34 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template shows the "Discount added" toast</t>
+          <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -6400,39 +6529,39 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-TMPL-010</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
+          <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6442,34 +6571,34 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
+          <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6484,34 +6613,34 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-010</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C28511</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Template admin — scoping</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -6526,34 +6655,34 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6568,39 +6697,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-001</t>
+          <t>FD-WO-005</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C28599</t>
+          <t>C28428</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays DISABLED until Name AND Type AND Calculation type AND Amount &gt; 0 are all set</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6610,34 +6739,34 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists</t>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-WO-013</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C28604</t>
+          <t>C28436</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify Max cap edge behavior — 0 or empty = no maximum, and Max Amount shows only for percentage methods</t>
+          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6652,24 +6781,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists</t>
+          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-WO-016</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C29441</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6679,12 +6808,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add dialog opens from the WO toolbar more (⋯) menu at Whole Work Order scope</t>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6694,91 +6823,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-005</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>C28428</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button is disabled until Name, Type, Calculation type and Amount&gt;0 are all set</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-013</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Verify whole-WO starting places are hidden without Work Orders: Create &amp; Edit</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists</t>
+          <t>/No TOGGLE (not a dropdown) — corrected. DEVIATION: the §5-R15 jurisdiction note is NOT shown below the Taxable toggle in this build (checked the whole-WO Add dialog with both Flat Amount and % of Subtotal; no note present — shots wo-03/wo-05). Expected kept as the spec requirement; currently a gap.</t>
         </is>
       </c>
     </row>
@@ -6814,8 +6859,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8253,7 +8296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8770,48 +8813,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-016</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>C29441</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the §5-R15 taxable jurisdiction note below the Taxable dropdown</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Pending — new case (V1_2 §5-R15 / S2-R26a); not yet checked live</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>NEW 2026-07-13 for V1_2 §5-R15 / S2-R26a. UI string check (advisory) — belongs in a FUNCTIONAL section, NOT an API section (standing rule 4). Assert the exact string verbatim.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -8825,7 +8826,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -706,7 +706,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage adjustment resolves as base × percent (10% fee on $150.00 → +$15.00)</t>
+          <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches</t>
+          <t>10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify percentage rounding — half a cent or more rounds UP (5% discount on $33.33 → $1.6665 → −$1.67)</t>
+          <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands</t>
+          <t>0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU.</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify a Flat Amount on Whole-WO or Labor Line resolves to the set amount exactly (no quantity multiplier)</t>
+          <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact</t>
+          <t>flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify a Flat Amount on a Part Line is PER ITEM (amount × quantity: $5.00 × qty 3 → −$15.00; qty 1 → −$5.00)</t>
+          <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>per-item: $2.00 x qty4 -&gt; $8.00 (part line)</t>
+          <t>per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried.</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount cannot exceed 100% (fee percentages have no upper limit)</t>
+          <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201)</t>
+          <t>discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount clamps a percentage result (20% fee on $100 → $20 → Max $15 → +$15.00)</t>
+          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00</t>
+          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 base resolves to $0.00 and the $0.00 line is skipped in QuickBooks (still shown on screens)</t>
+          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10% of $0 parts -&gt; $0.00</t>
+          <t>10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied.</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify a negative base is treated as $0 (resolved amount = $0.00, base never goes below zero)</t>
+          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50% discount on $0 base -&gt; $0.00; base floored at 0</t>
+          <t>50% discount on $0 base -&gt; $0.00; base floored at 0 | WORDING+VIU 2026-07-13: Base-floor-at-$0 carried; build labels. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable adjustment does not change tax</t>
+          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands</t>
+          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No).</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify the 3-step resolution ORDER — line-level on gross first, whole-WO on net second, no stacking within a step</t>
+          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3-step order re-proven: whole-WO 10% resolved 17.08 alone -&gt; 19.08 after a $20 labor-line fee (+10% of the line-level effect); whole-WO adjs do not stack on each other (17.08 each)</t>
+          <t>3-step order re-proven: whole-WO 10% resolved 17.08 alone -&gt; 19.08 after a $20 labor-line fee (+10% of the line-level effect); whole-WO adjs do not stack on each other (17.08 each) | WORDING+VIU 2026-07-13: 3-step order carried; build labels.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400)</t>
+          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify negative-total floor at $0.00 — non-taxable $150 discount on $100 parts + $10 tax: subtotal floors, customer pays $10, $50 excess → tax-exempt goodwill credit</t>
+          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact</t>
+          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels.</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify a TAXABLE $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured</t>
+          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels.</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer "Fees &amp; Discounts (N)" tab shows the correct default count</t>
+          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults)</t>
+          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify the "Default Fees &amp; Discounts" card header, caption, and table columns</t>
+          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,24 +1309,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…')</t>
+          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-008</t>
+          <t>FD-CUST-003</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28492</t>
+          <t>C28487</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
+          <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1351,39 +1351,39 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>empty-state card re-observed on a 0-default customer</t>
+          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-009</t>
+          <t>FD-CUST-004</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28493</t>
+          <t>C28488</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify a customer default is added as an independent adjustment on every NEW work order</t>
+          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1393,39 +1393,39 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default)</t>
+          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-010</t>
+          <t>FD-CUST-007</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28494</t>
+          <t>C28491</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage customer default re-resolves per work order (keeps percent, not a fixed dollar)</t>
+          <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1435,39 +1435,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO</t>
+          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-011</t>
+          <t>FD-CUST-008</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C28495</t>
+          <t>C28492</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default does NOT change adjustments already on existing work orders</t>
+          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1477,34 +1477,34 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>removing the default link leaves the existing WO's adjustment intact</t>
+          <t>empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-012</t>
+          <t>FD-CUST-009</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C28496</t>
+          <t>C28493</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template that is a customer default drops the default link but keeps existing WO adjustments</t>
+          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1519,39 +1519,39 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>deleting a linked template (204) cascades the default link away</t>
+          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-013</t>
+          <t>FD-CUST-010</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C28497</t>
+          <t>C28494</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a customer removes that customer's default links</t>
+          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1561,39 +1561,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature</t>
+          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-014</t>
+          <t>FD-CUST-011</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C28498</t>
+          <t>C28495</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults seeding</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify a newly created customer inherits every auto-apply location template as a default</t>
+          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1603,34 +1603,34 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded)</t>
+          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-015</t>
+          <t>FD-CUST-012</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C28499</t>
+          <t>C28496</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — permissions</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer Fees &amp; Discounts tab and controls are hidden without the required permissions</t>
+          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1645,39 +1645,39 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat)</t>
+          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-016</t>
+          <t>FD-CUST-013</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C28500</t>
+          <t>C28497</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults — known bug</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only ONCE to a new WO</t>
+          <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1687,39 +1687,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>template BOTH auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (appliedBy=customer_default)</t>
+          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-017</t>
+          <t>FD-CUST-014</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>C28501</t>
+          <t>C28498</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — negative</t>
+          <t>Customer defaults seeding</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1729,34 +1729,34 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>bad-template add 400 / bad-customer load 404 / bad remove 404</t>
+          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-001</t>
+          <t>FD-CUST-015</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C28533</t>
+          <t>C28499</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1771,39 +1771,39 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present</t>
+          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-002</t>
+          <t>FD-CUST-016</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C28534</t>
+          <t>C28500</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer defaults — known bug</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
+          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1813,39 +1813,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present)</t>
+          <t>template BOTH auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Double-add once (BUG-FD-1 not reproduced); build labels.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-003</t>
+          <t>FD-CUST-017</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C28535</t>
+          <t>C28501</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1855,34 +1855,34 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase)</t>
+          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-004</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C28536</t>
+          <t>C28533</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Customer document — amount format</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1897,34 +1897,34 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed</t>
+          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-005</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C28537</t>
+          <t>C28534</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1939,39 +1939,39 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc)</t>
+          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-006</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C28538</t>
+          <t>C28535</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1981,39 +1981,39 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target</t>
+          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-007</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C28539</t>
+          <t>C28536</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2023,39 +2023,39 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines)</t>
+          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-008</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C28540</t>
+          <t>C28537</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
+          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2065,39 +2065,39 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895)</t>
+          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-009</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C28541</t>
+          <t>C28538</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2107,34 +2107,34 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0</t>
+          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-010</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C28542</t>
+          <t>C28539</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2149,34 +2149,34 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock)</t>
+          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-011</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>C28543</t>
+          <t>C28540</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Customer document — layout</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2191,39 +2191,39 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope)</t>
+          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-001</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>C28476</t>
+          <t>C28541</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2233,34 +2233,34 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit.</t>
+          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-002</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>C28477</t>
+          <t>C28542</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2275,34 +2275,34 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01).</t>
+          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-003</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>C28478</t>
+          <t>C28543</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2317,34 +2317,34 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
+          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-001</t>
+          <t>FD-EDIT-001</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C28464</t>
+          <t>C28476</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
+          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2359,34 +2359,34 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03).</t>
+          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-002</t>
+          <t>FD-EDIT-002</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>C28465</t>
+          <t>C28477</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
+          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2401,34 +2401,34 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
+          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-003</t>
+          <t>FD-EDIT-003</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>C28466</t>
+          <t>C28478</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
+          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2443,34 +2443,34 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
+          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-FIN-001</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>C28467</t>
+          <t>C28464</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2485,34 +2485,34 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate.</t>
+          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-FIN-002</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>C28468</t>
+          <t>C28465</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
+          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2527,39 +2527,39 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'.</t>
+          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-001</t>
+          <t>FD-FIN-003</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>C28454</t>
+          <t>C28466</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2569,34 +2569,34 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03).</t>
+          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-002</t>
+          <t>FD-FIN-004</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>C28455</t>
+          <t>C28467</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2611,34 +2611,34 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03).</t>
+          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-004</t>
+          <t>FD-FIN-005</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C28457</t>
+          <t>C28468</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2653,39 +2653,39 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned.</t>
+          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-005</t>
+          <t>FD-HIST-001</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>C28458</t>
+          <t>C28560</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
+          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2695,34 +2695,34 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
+          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-002</t>
+          <t>FD-HIST-002</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C28440</t>
+          <t>C28561</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line % of Labor Total fee resolves against the line's gross labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2737,34 +2737,34 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands</t>
+          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-003</t>
+          <t>FD-HIST-003</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C28441</t>
+          <t>C28562</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row exposes its own 3-dot menu on hover</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2779,34 +2779,34 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API</t>
+          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-004</t>
+          <t>FD-HIST-005</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C28442</t>
+          <t>C28564</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>History log — visibility</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line Flat Amount resolves to the exact amount with no quantity multiplier</t>
+          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2821,39 +2821,39 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier</t>
+          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-005</t>
+          <t>FD-HIST-006</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>C28443</t>
+          <t>C28565</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>History log — permission</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment resolves to $0.00 when its line is not billable (declined)</t>
+          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2863,34 +2863,34 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500)</t>
+          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-006</t>
+          <t>FD-HIST-007</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C28444</t>
+          <t>C28566</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>History log — Processing Fee</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any adjustment pointing to it</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2905,39 +2905,39 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide)</t>
+          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-007</t>
+          <t>FD-HIST-008</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C28445</t>
+          <t>C28567</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>History log — edit entry</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line 'Add fee / discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2947,39 +2947,39 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives</t>
+          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-002</t>
+          <t>FD-INLINE-001</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C28447</t>
+          <t>C28454</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line Flat Amount is charged PER ITEM (amount × quantity): $5.00 × qty 3 → −$15.00</t>
+          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2989,34 +2989,34 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00')</t>
+          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-003</t>
+          <t>FD-INLINE-002</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>C28448</t>
+          <t>C28455</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
+          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3031,39 +3031,39 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500)</t>
+          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-004</t>
+          <t>FD-INLINE-004</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C28449</t>
+          <t>C28457</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line % of Parts Total resolves against quantity × sell price (gross)</t>
+          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3073,34 +3073,34 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08</t>
+          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-006</t>
+          <t>FD-INLINE-005</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C28451</t>
+          <t>C28458</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3115,39 +3115,39 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock)</t>
+          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-007</t>
+          <t>FD-LABOR-001</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C28452</t>
+          <t>C28439</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any adjustment pointing to it</t>
+          <t>Verify a labor line's ⋮ menu opens the Add Fee/Discount dialog locked to that labor line</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3157,39 +3157,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>prior delete-cascade (batch-4) stands; not re-seedable today</t>
+          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-008</t>
+          <t>FD-LABOR-002</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>C28453</t>
+          <t>C28440</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify per-item Flat Amount edge: quantity 1 resolves to the base amount (−$5.00)</t>
+          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3199,39 +3199,39 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4</t>
+          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-LABOR-003</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C28585</t>
+          <t>C28441</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
+          <t>Verify each labor line row shows its own ⋮ menu on hover</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3241,39 +3241,39 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00')</t>
+          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-LABOR-004</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28442</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3283,39 +3283,39 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat)</t>
+          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-LABOR-005</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28443</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
+          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3325,39 +3325,39 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed)</t>
+          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-LABOR-006</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28444</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
+          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3367,39 +3367,39 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency)</t>
+          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-LABOR-007</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28445</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
+          <t>Verify the labor-line 'Add Fee/Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3409,39 +3409,39 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403</t>
+          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PART-001</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28446</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify a part's ⋮ menu opens the Add Fee/Discount dialog locked to that part</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3451,39 +3451,39 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403</t>
+          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PART-002</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28447</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
+          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3493,39 +3493,39 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON)</t>
+          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PART-003</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28448</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3535,34 +3535,34 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock)</t>
+          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PART-004</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C28449</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3577,39 +3577,39 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope</t>
+          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PART-006</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28451</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3619,34 +3619,34 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto)</t>
+          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PART-007</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28452</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify deleting a part removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3661,34 +3661,34 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5)</t>
+          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PART-008</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28453</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3703,39 +3703,39 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee'</t>
+          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28585</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3745,39 +3745,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0)</t>
+          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3787,39 +3787,39 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time)</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3829,39 +3829,39 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3871,34 +3871,34 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00</t>
+          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3955,39 +3955,39 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-PERM-009</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28593</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
+          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3997,39 +3997,39 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4039,39 +4039,39 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple adjustments on one part each resolve on the part's own base (do not compound) and net correctly</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4081,34 +4081,34 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding)</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-WO percentage adjustments resolve against the same net totals and do not change each other's base</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4123,39 +4123,39 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding)</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template').</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4207,34 +4207,34 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4249,39 +4249,39 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the delete action</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4291,39 +4291,39 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4333,39 +4333,39 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog copy and buttons</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4375,39 +4375,39 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4417,39 +4417,39 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact)</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4459,39 +4459,39 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4501,39 +4501,39 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts'</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure toast</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4543,39 +4543,39 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced)</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4585,39 +4585,39 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify template Name enforces the 100-character limit</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -4627,34 +4627,34 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4669,34 +4669,34 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4711,34 +4711,34 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts').</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4753,34 +4753,34 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4837,39 +4837,39 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4879,39 +4879,39 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4921,39 +4921,39 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4963,34 +4963,34 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5005,34 +5005,34 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5047,39 +5047,39 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5089,34 +5089,34 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5131,39 +5131,39 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5173,34 +5173,34 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5215,39 +5215,39 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -5257,39 +5257,39 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5299,39 +5299,39 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -5341,47 +5341,803 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>FD-TMPL-017</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>C28518</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — dialog fields</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Verify the template Name is limited to 100 characters</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-002</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>C28600</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-003</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>C28601</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-004</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>C28602</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-005</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>C28603</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-007</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>C28605</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-001</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>C28424</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-002</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>C28425</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-003</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>C28426</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-004</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>C28427</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-006</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>C28429</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-007</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>C28430</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-008</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>C28431</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-009</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>C28432</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-010</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>C28433</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-011</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>C28434</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-012</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>C28435</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-014</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>C28437</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-015</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>C28438</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass.</t>
         </is>
@@ -5501,6 +6257,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5512,7 +6286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5590,7 +6364,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify minimum values — Flat Amount smallest is $0.01, Percentage smallest is 0.01%</t>
+          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -5605,7 +6379,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected</t>
+          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied.</t>
         </is>
       </c>
     </row>
@@ -5632,7 +6406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount = $0 forces resolve to $0.00, while blank/empty Max Amount means no cap</t>
+          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -5647,7 +6421,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00)</t>
+          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied.</t>
         </is>
       </c>
     </row>
@@ -5674,7 +6448,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee resolves LAST on the tax-inclusive Grand Total (3% of $324 → +$9.72)</t>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -5689,24 +6463,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent</t>
+          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-003</t>
+          <t>FD-CUST-005</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>C28487</t>
+          <t>C28489</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -5716,12 +6490,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a single template as a customer default via the picker</t>
+          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5731,24 +6505,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update)</t>
+          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-004</t>
+          <t>FD-CUST-006</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28488</t>
+          <t>C28490</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -5758,12 +6532,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
+          <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5773,39 +6547,39 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending</t>
+          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-005</t>
+          <t>FD-INLINE-003</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28489</t>
+          <t>C28456</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify the picker lists only unlinked templates and shows Processing Fee templates as type "Fee"</t>
+          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5815,39 +6589,39 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending</t>
+          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-006</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28490</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify the empty picker message when there are no templates left to add</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5857,34 +6631,34 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-007</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28491</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default via the row's remove action needs no confirm and toasts</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -5899,34 +6673,34 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-003</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28456</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5941,39 +6715,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-001</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28439</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's 3-dot menu opens the Add dialog locked to that Labor Line scope</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5983,39 +6757,39 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-001</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28446</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
+          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6025,39 +6799,39 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-002</t>
+          <t>FD-STATS-002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify each Stats fee/discount row names its target</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6067,39 +6841,39 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision)</t>
+          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-008</t>
+          <t>FD-STATS-004</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28526</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a WO can be removed but not edited</t>
+          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6109,34 +6883,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift)</t>
+          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-009</t>
+          <t>FD-TMPL-010</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -6151,39 +6925,39 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6193,34 +6967,34 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-001</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28459</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6235,34 +7009,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01).</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-002</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28460</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify each Stats fee/discount row names its target</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6277,39 +7051,39 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-004</t>
+          <t>FD-WO-005</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28462</t>
+          <t>C28428</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6319,39 +7093,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-WO-013</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28436</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
+          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6361,39 +7135,39 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target)</t>
+          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-WO-016</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C29441</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6402,426 +7176,6 @@
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-004</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>C28505</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — create</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Verify creating a Discount template shows the "Discount added" toast</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-006</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>C28507</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — edit</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-008</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>C28509</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — delete</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-010</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>C28511</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — scoping</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-011</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>C28512</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — dialog fields</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>FD-VAL-001</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>C28599</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>FD-VAL-006</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>C28604</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-005</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>C28428</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-013</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-016</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>C29441</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>/No TOGGLE (not a dropdown) — corrected. DEVIATION: the §5-R15 jurisdiction note is NOT shown below the Taxable toggle in this build (checked the whole-WO Add dialog with both Flat Amount and % of Subtotal; no note present — shots wo-03/wo-05). Expected kept as the spec requirement; currently a gap.</t>
         </is>
@@ -6849,16 +7203,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6948,7 +7292,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single adjustment's name and rate</t>
+          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -6963,7 +7307,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale)</t>
+          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
         </is>
       </c>
     </row>
@@ -6990,7 +7334,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has multiple adjustments</t>
+          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has several fees/discounts</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -7005,7 +7349,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today)</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7376,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no adjustments</t>
+          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no fees/discounts</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -7047,7 +7391,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today)</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7418,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking a populated 'Fees &amp; Discounts' cell opens the per-part breakdown modal with the correct columns</t>
+          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7089,7 +7433,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today)</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7460,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify the breakdown modal 'Net adjustment' row equals the signed sum of the part's adjustments</t>
+          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7131,7 +7475,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today)</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7502,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify a per-row Remove (trash) on the breakdown modal removes the adjustment and closes the modal when the last is removed</t>
+          <t>Verify a per-row Remove on the breakdown removes the fee/discount and closes when the last one is removed</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7173,7 +7517,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today)</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7544,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify the '+ Add' button is disabled on a part when the sale/WO cannot be edited</t>
+          <t>Verify the '+ Add' button is disabled when the sale/work order cannot be edited</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7215,7 +7559,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today)</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7586,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify Part-Sale adjustment add/edit/remove (whole sale or part line) requires Part Sales: Create and Edit + See Financial Data</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7257,7 +7601,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Part Sales adjustment surface absent (Story 11 re-checked today)</t>
+          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate.</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7628,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify "Processing Fee" is a third type in the template builder (template-only)</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -7299,7 +7643,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog)</t>
+          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7670,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount (default) and % of Grand Total, with a tax-inclusive base</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7341,7 +7685,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee)</t>
+          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7712,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for every Processing Fee (both methods)</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -7383,7 +7727,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400)</t>
+          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7754,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable control defaults Yes and shows the §5-R15 jurisdiction note</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7420,12 +7764,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt (expected rewritten to §5-R15 jurisdiction note per S8-R13; re-check when Story-8 builder ships)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today)</t>
+          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7532,7 +7876,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple discount lines are penny-capped via largest-remainder so capped discounts sum exactly to the floored net subtotal (no negative, whole-cent)</t>
+          <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -7547,7 +7891,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>floor half RE-PROVEN (stacked 120+100 on 182.76 -&gt; sub 0.00, excess 37.24 exact); QB penny-cap half needs QB-side line view</t>
+          <t>floor half RE-PROVEN (stacked 120+100 on 182.76 -&gt; sub 0.00, excess 37.24 exact); QB penny-cap half needs QB-side line view | WORDING+VIU 2026-07-13: BLOCKED-ENV: the QuickBooks penny-cap (largest-remainder) allocation on discount lines is only observable inside QuickBooks (no QB read API; export currently fails on duplicate document numbers). The in-app $0.00 floor half is verified. Build labels applied.</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7918,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify with the FeesAndDiscounts flag OFF, all F&amp;D UI and behavior are hidden everywhere</t>
+          <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -7589,24 +7933,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>org flag toggling deliberately NOT done: shared env, manual tester active today</t>
+          <t>org flag toggling deliberately NOT done: shared env, manual tester active today | WORDING+VIU 2026-07-13: BLOCKED-ENV: cannot take a feature-off window on the shared qb env while a manual tester is active. Wording made layman.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FD-FLAG-003</t>
+          <t>FD-FLAG-002</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>C28598</t>
+          <t>C28597</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -7616,7 +7960,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify with the flag ON, the matching permission is still required to use F&amp;D</t>
+          <t>Verify the work-order history still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -7631,39 +7975,39 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>as FD-FLAG-001; the flag-ON half of the AND-gate is fresh-proven (FD-PERM-010)</t>
+          <t>as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV + V1_2 re-VIU pending: needs a feature-off window (not takeable on the shared env) to confirm history entries stay visible. Wording made layman.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-001</t>
+          <t>FD-FLAG-003</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>C28544</t>
+          <t>C28598</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync</t>
+          <t>Feature-flag gating</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee +, discount −)</t>
+          <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7673,34 +8017,34 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>QB invoice line internals unobservable (no read API; export of re-invoiced WOs fails on duplicate doc numbers) — needs QB-UI eyeball of a cleanly synced invoice</t>
+          <t>as FD-FLAG-001; the flag-ON half of the AND-gate is fresh-proven (FD-PERM-010) | WORDING+VIU 2026-07-13: BLOCKED-ENV (permission half): the See-Financial-Data masking half is established, but the full both-gates check needs a restricted-role login — re-run after the roles matrix is re-derived. Wording made layman.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-002</t>
+          <t>FD-HIST-004</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28545</t>
+          <t>C28563</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync</t>
+          <t>History log — visibility</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify the QuickBooks line description equals the adjustment name and the item is the mapped Fee/Discount item</t>
+          <t>Verify fee/discount history stays visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7715,39 +8059,39 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-001 — needs QB UI (generic Fee/Discount item + description=name)</t>
+          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV: needs a feature-off window (not takeable on the shared env with a live tester).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-003</t>
+          <t>FD-QB-001</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28546</t>
+          <t>C28544</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync — edge</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 resolved adjustment is skipped when sent to QuickBooks</t>
+          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7757,34 +8101,34 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-001 — $0-line skip only visible QB-side</t>
+          <t>QB invoice line internals unobservable (no read API; export of re-invoiced WOs fails on duplicate doc numbers) — needs QB-UI eyeball of a cleanly synced invoice | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-004</t>
+          <t>FD-QB-002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28547</t>
+          <t>C28545</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a fee is blocked when the Fee item is unmapped (exact message)</t>
+          <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7799,39 +8143,39 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>unmap not achievable today: PUT bookkeeping/settings {settings:{feeItemId:null}} -&gt; 500 (requestId 4bd14847); flat payload -&gt; 400 'settings missing'. Mapping stayed connected+mapped (verified). Guard cycle needs a working unmap (dev/QB-side)</t>
+          <t>as FD-QB-001 — needs QB UI (generic Fee/Discount item + description=name) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-005</t>
+          <t>FD-QB-003</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28548</t>
+          <t>C28546</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard</t>
+          <t>QuickBooks sync — edge</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a discount is blocked when the Discount item is unmapped (exact message)</t>
+          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7841,39 +8185,39 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004 (unmap 500)</t>
+          <t>as FD-QB-001 — $0-line skip only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-006</t>
+          <t>FD-QB-004</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28549</t>
+          <t>C28547</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard scope</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify the mapping guard blocks adds on every add surface (WO, labor line, part, part sale, template-apply)</t>
+          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7883,39 +8227,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004 (unmap 500)</t>
+          <t>unmap not achievable today: PUT bookkeeping/settings {settings:{feeItemId:null}} -&gt; 500 (requestId 4bd14847); flat payload -&gt; 400 'settings missing'. Mapping stayed connected+mapped (verified). Guard cycle needs a working unmap (dev/QB-side) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-007</t>
+          <t>FD-QB-005</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28550</t>
+          <t>C28548</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard (auto-apply)</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify an auto-apply default cannot be saved while the matching QuickBooks item is unmapped</t>
+          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7925,34 +8269,34 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004 (unmap 500)</t>
+          <t>as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-008</t>
+          <t>FD-QB-006</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28551</t>
+          <t>C28549</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard exceptions</t>
+          <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify creating/editing a non-auto-apply template is always allowed and no block exists when QuickBooks is not connected</t>
+          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -7967,34 +8311,34 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004; positive half (template create while MAPPED) works throughout</t>
+          <t>as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-009</t>
+          <t>FD-QB-007</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28552</t>
+          <t>C28550</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — unmap recovery</t>
+          <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify unmapping an in-use item routes affected invoices to Unexported Items (recoverable, no data lost)</t>
+          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8009,39 +8353,39 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>unexported-items list + retry + mark-done endpoints re-exercised (mark-done 200 on my entries); the unmap-in-flight repro blocked by the unmap 500</t>
+          <t>as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-010</t>
+          <t>FD-QB-008</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28553</t>
+          <t>C28551</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class</t>
+          <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify a single QuickBooks Class applies to every synced line including fee/discount lines</t>
+          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,39 +8395,39 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Class application only visible QB-side</t>
+          <t>as FD-QB-004; positive half (template create while MAPPED) works throughout | WORDING+VIU 2026-07-13: Observable half CONFIRMED live: creating a non-auto-apply template is always allowed (template create 201). The 'no block when QuickBooks not connected' half is Blocked-Env — QuickBooks is connected here and cannot be disconnected on the shared env.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-011</t>
+          <t>FD-QB-009</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28554</t>
+          <t>C28552</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class validation</t>
+          <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify a deleted/deactivated Class aborts the entire invoice sync (no substitution)</t>
+          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8093,39 +8437,39 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>stale-Class abort only reproducible QB-side</t>
+          <t>unexported-items list + retry + mark-done endpoints re-exercised (mark-done 200 on my entries); the unmap-in-flight repro blocked by the unmap 500 | WORDING+VIU 2026-07-13:  BLOCKED-ENV: cannot unmap an in-use item — the unmap call 500s on this env — so the route-to-Unexported-Items behavior can't be driven. (The Unexported Items list itself is reachable and returns data.)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-013</t>
+          <t>FD-QB-010</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28556</t>
+          <t>C28553</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>QuickBooks — Class</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify discount lines to QuickBooks are capped with largest-remainder whole-cent penny allocation</t>
+          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8135,39 +8479,39 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>penny-cap allocation of discount LINES only visible on QB invoice lines</t>
+          <t>Class application only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-015</t>
+          <t>FD-QB-011</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28558</t>
+          <t>C28554</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>QuickBooks — Class validation</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit memo</t>
+          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8177,34 +8521,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>IN-APP HALF VERIFIED TODAY: invoicing the over-discounted WO recorded a CUSTOMER CREDIT (unpaid-transactions 2-&gt;4; 'current' bucket -11.63 -&gt; -119.73 = +9.14 invoice &amp; -117.24 credit exactly). QB goodwill-memo half unobservable: invoice export fails on the duplicate-doc-number env bug, no credit_memo export fired, no QB read API — needs QB UI on a cleanly synced org</t>
+          <t>stale-Class abort only reproducible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-016</t>
+          <t>FD-QB-013</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28559</t>
+          <t>C28556</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync — tax</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify a synced line's tax follows the adjustment's taxable setting</t>
+          <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -8219,49 +8563,133 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>tax code on the QB line unobservable in-app; in-app taxable base shifts re-proven (FD-CALC-011)</t>
+          <t>penny-cap allocation of discount LINES only visible on QB invoice lines | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the largest-remainder penny allocation on the QuickBooks discount lines is only visible inside QuickBooks (same as FD-CALC-017). The in-app $0.00 floor half is verified.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>FD-QB-015</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>C28558</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks — negative totals</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>IN-APP HALF VERIFIED TODAY: invoicing the over-discounted WO recorded a CUSTOMER CREDIT (unpaid-transactions 2-&gt;4; 'current' bucket -11.63 -&gt; -119.73 = +9.14 invoice &amp; -117.24 credit exactly). QB goodwill-memo half unobservable: invoice export fails on the duplicate-doc-number env bug, no credit_memo export fired, no QB read API — needs QB UI on a cleanly synced org | WORDING+VIU 2026-07-13: In-app customer-credit half VERIFIED 2026-07-10 (invoicing an over-discounted WO recorded a customer credit of exactly the excess). BLOCKED-ENV: the QuickBooks tax-exempt goodwill credit-memo half needs a human in QuickBooks (export fails on duplicate document numbers; no QB read API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FD-QB-016</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>C28559</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks sync — tax</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>tax code on the QB line unobservable in-app; in-app taxable base shifts re-proven (FD-CALC-011) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>FD-TMPL-012</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>C28513</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active)</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance.</t>
         </is>
       </c>
     </row>
@@ -8285,6 +8713,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8296,7 +8726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8354,27 +8784,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FD-FLAG-002</t>
+          <t>FD-PART-005</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>C28597</t>
+          <t>C28450</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Feature-flag gating</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify the WO history log STILL shows fee/discount entries even when the feature flag is OFF</t>
+          <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -8384,448 +8814,18 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-001</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>C28560</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>History log</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-002</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>C28561</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>History log</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify the history detail block shows Name, Type, Amount (set rate), and Applied-to label</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-003</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>C28562</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>History log</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify an adjustment entry leaves the saved-state icon empty and the Line column shows "−"</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-004</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>C28563</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>History log — visibility</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the feature flag</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-005</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>C28564</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>History log — visibility</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verify F&amp;D history stays visible when the F&amp;D UI is hidden by See Financial Data being off</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-006</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>C28565</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>History log — permission</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-007</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>C28566</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>History log — Processing Fee</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee is logged as a fee with "Full invoice" applied-to and no "updated" entry</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-008</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>C28567</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>History log — edit entry</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>FD-PART-005</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>C28450</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Verify a part-line adjustment stays attached when the part changes from requested to received</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>FD-PERM-009</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>C28593</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify seeing fee/discount entries in the WO history log requires Work Orders: Create and Edit (line history requires Work Order Lines: Create and Edit)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V1_2 S13-R10, needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU.</t>
+          <t>STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order | WORDING+VIU 2026-07-13: BLOCKED/PENDING: requested→received transition blocked by the env-wide WO line-create 500 + completed-line part-request lock — cannot drive the transition. Build labels applied.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -896,17 +896,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-007</t>
+          <t>FD-CALC-006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28574</t>
+          <t>C28573</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28574</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28573</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
+          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -931,24 +931,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
+          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-009</t>
+          <t>FD-CALC-007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28576</t>
+          <t>C28574</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28576</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28574</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
+          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied.</t>
+          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-010</t>
+          <t>FD-CALC-008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28577</t>
+          <t>C28575</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28577</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28575</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
+          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1015,24 +1015,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50% discount on $0 base -&gt; $0.00; base floored at 0 | WORDING+VIU 2026-07-13: Base-floor-at-$0 carried; build labels. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
+          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-011</t>
+          <t>FD-CALC-009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28578</t>
+          <t>C28576</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28578</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28576</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
+          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1057,24 +1057,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No).</t>
+          <t>10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-012</t>
+          <t>FD-CALC-010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28579</t>
+          <t>C28577</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28579</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28577</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
+          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3-step order re-proven: whole-WO 10% resolved 17.08 alone -&gt; 19.08 after a $20 labor-line fee (+10% of the line-level effect); whole-WO adjs do not stack on each other (17.08 each) | WORDING+VIU 2026-07-13: 3-step order carried; build labels.</t>
+          <t>50% discount on $0 base -&gt; $0.00; base floored at 0 | WORDING+VIU 2026-07-13: Base-floor-at-$0 carried; build labels. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-014</t>
+          <t>FD-CALC-011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28581</t>
+          <t>C28578</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28578</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
+          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1141,24 +1141,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels.</t>
+          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-015</t>
+          <t>FD-CALC-012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28582</t>
+          <t>C28579</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28579</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
+          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels.</t>
+          <t>3-step order re-proven: whole-WO 10% resolved 17.08 alone -&gt; 19.08 after a $20 labor-line fee (+10% of the line-level effect); whole-WO adjs do not stack on each other (17.08 each) | WORDING+VIU 2026-07-13: 3-step order carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-016</t>
+          <t>FD-CALC-014</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28583</t>
+          <t>C28581</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1225,34 +1225,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels.</t>
+          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-001</t>
+          <t>FD-CALC-015</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28485</t>
+          <t>C28582</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
+          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1267,39 +1267,39 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
+          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-002</t>
+          <t>FD-CALC-016</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28486</t>
+          <t>C28583</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
+          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1309,24 +1309,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
+          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-003</t>
+          <t>FD-CUST-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28487</t>
+          <t>C28485</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a single template as a customer default via the picker</t>
+          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
+          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-004</t>
+          <t>FD-CUST-002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28488</t>
+          <t>C28486</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
+          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1393,24 +1393,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
+          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-007</t>
+          <t>FD-CUST-003</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28491</t>
+          <t>C28487</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default from the row needs no confirmation</t>
+          <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1435,24 +1435,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
+          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-008</t>
+          <t>FD-CUST-004</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C28492</t>
+          <t>C28488</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
+          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1477,34 +1477,34 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
+          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-009</t>
+          <t>FD-CUST-007</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C28493</t>
+          <t>C28491</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
+          <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1519,39 +1519,39 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card).</t>
+          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-010</t>
+          <t>FD-CUST-008</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C28494</t>
+          <t>C28492</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
+          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1561,34 +1561,34 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
+          <t>empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-011</t>
+          <t>FD-CUST-009</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C28495</t>
+          <t>C28493</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
+          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1603,39 +1603,39 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204).</t>
+          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-012</t>
+          <t>FD-CUST-010</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C28496</t>
+          <t>C28494</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
+          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1645,24 +1645,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried.</t>
+          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-013</t>
+          <t>FD-CUST-011</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C28497</t>
+          <t>C28495</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a customer removes that customer's default links</t>
+          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1687,39 +1687,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried.</t>
+          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-014</t>
+          <t>FD-CUST-012</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>C28498</t>
+          <t>C28496</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults seeding</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
+          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1729,39 +1729,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
+          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-015</t>
+          <t>FD-CUST-013</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C28499</t>
+          <t>C28497</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — permissions</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
+          <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1771,34 +1771,34 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
+          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-016</t>
+          <t>FD-CUST-014</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C28500</t>
+          <t>C28498</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults — known bug</t>
+          <t>Customer defaults seeding</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
+          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1813,39 +1813,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>template BOTH auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Double-add once (BUG-FD-1 not reproduced); build labels.</t>
+          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-017</t>
+          <t>FD-CUST-015</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C28501</t>
+          <t>C28499</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — negative</t>
+          <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1855,39 +1855,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
+          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-001</t>
+          <t>FD-CUST-016</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C28533</t>
+          <t>C28500</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Customer defaults — known bug</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1897,39 +1897,39 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
+          <t>template BOTH auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Double-add once (BUG-FD-1 not reproduced); build labels.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-002</t>
+          <t>FD-CUST-017</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C28534</t>
+          <t>C28501</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1939,39 +1939,39 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
+          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-003</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C28535</t>
+          <t>C28533</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1981,34 +1981,34 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
+          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-004</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C28536</t>
+          <t>C28534</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Customer document — amount format</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2023,39 +2023,39 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
+          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-005</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C28537</t>
+          <t>C28535</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2065,34 +2065,34 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
+          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-006</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C28538</t>
+          <t>C28536</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2107,39 +2107,39 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
+          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-007</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C28539</t>
+          <t>C28537</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2149,39 +2149,39 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
+          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-008</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>C28540</t>
+          <t>C28538</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2191,39 +2191,39 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
+          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-009</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>C28541</t>
+          <t>C28539</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2233,34 +2233,34 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
+          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-010</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>C28542</t>
+          <t>C28540</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2275,39 +2275,39 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
+          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-011</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>C28543</t>
+          <t>C28541</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Customer document — layout</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2317,39 +2317,39 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
+          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-001</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C28476</t>
+          <t>C28542</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2359,34 +2359,34 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit.</t>
+          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-002</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>C28477</t>
+          <t>C28543</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2401,24 +2401,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01).</t>
+          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-003</t>
+          <t>FD-EDIT-001</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>C28478</t>
+          <t>C28476</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2428,12 +2428,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
+          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2443,39 +2443,39 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
+          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-001</t>
+          <t>FD-EDIT-002</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>C28464</t>
+          <t>C28477</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
+          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2485,34 +2485,34 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03).</t>
+          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-002</t>
+          <t>FD-EDIT-003</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>C28465</t>
+          <t>C28478</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
+          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2527,24 +2527,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
+          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-003</t>
+          <t>FD-FIN-001</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>C28466</t>
+          <t>C28464</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2569,39 +2569,39 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
+          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-FIN-002</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>C28467</t>
+          <t>C28465</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
+          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2611,34 +2611,34 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate.</t>
+          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-FIN-003</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C28468</t>
+          <t>C28466</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
+          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2653,34 +2653,34 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'.</t>
+          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-001</t>
+          <t>FD-FIN-004</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>C28560</t>
+          <t>C28467</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2695,39 +2695,39 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type.</t>
+          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-002</t>
+          <t>FD-FIN-005</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C28561</t>
+          <t>C28468</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2737,24 +2737,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate).</t>
+          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-003</t>
+          <t>FD-HIST-001</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C28562</t>
+          <t>C28560</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
+          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2779,39 +2779,39 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01).</t>
+          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-005</t>
+          <t>FD-HIST-002</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C28564</t>
+          <t>C28561</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2821,39 +2821,39 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it.</t>
+          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-006</t>
+          <t>FD-HIST-003</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>C28565</t>
+          <t>C28562</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>History log — permission</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2863,34 +2863,34 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate).</t>
+          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-007</t>
+          <t>FD-HIST-005</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C28566</t>
+          <t>C28564</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>History log — Processing Fee</t>
+          <t>History log — visibility</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
+          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2905,39 +2905,39 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry.</t>
+          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-008</t>
+          <t>FD-HIST-006</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C28567</t>
+          <t>C28565</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>History log — edit entry</t>
+          <t>History log — permission</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2947,39 +2947,39 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate).</t>
+          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-001</t>
+          <t>FD-HIST-007</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C28454</t>
+          <t>C28566</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>History log — Processing Fee</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2989,39 +2989,39 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03).</t>
+          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-002</t>
+          <t>FD-HIST-008</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>C28455</t>
+          <t>C28567</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>History log — edit entry</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3031,24 +3031,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03).</t>
+          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-004</t>
+          <t>FD-INLINE-001</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C28457</t>
+          <t>C28454</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
+          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3073,24 +3073,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned.</t>
+          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-005</t>
+          <t>FD-INLINE-002</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C28458</t>
+          <t>C28455</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
+          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3115,39 +3115,39 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
+          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-001</t>
+          <t>FD-INLINE-004</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C28439</t>
+          <t>C28457</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's ⋮ menu opens the Add Fee/Discount dialog locked to that labor line</t>
+          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3157,39 +3157,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
+          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-002</t>
+          <t>FD-INLINE-005</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>C28440</t>
+          <t>C28458</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3199,24 +3199,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
+          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-003</t>
+          <t>FD-LABOR-001</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C28441</t>
+          <t>C28439</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row shows its own ⋮ menu on hover</t>
+          <t>Verify a labor line's ⋮ menu opens the Add Fee/Discount dialog locked to that labor line</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
+          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-004</t>
+          <t>FD-LABOR-002</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C28442</t>
+          <t>C28440</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
+          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3283,24 +3283,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried.</t>
+          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-005</t>
+          <t>FD-LABOR-003</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C28443</t>
+          <t>C28441</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
+          <t>Verify each labor line row shows its own ⋮ menu on hover</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3325,24 +3325,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
+          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-006</t>
+          <t>FD-LABOR-004</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C28444</t>
+          <t>C28442</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
+          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3367,24 +3367,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels.</t>
+          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-007</t>
+          <t>FD-LABOR-005</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C28445</t>
+          <t>C28443</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify the labor-line 'Add Fee/Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3409,39 +3409,39 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived.</t>
+          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-001</t>
+          <t>FD-LABOR-006</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C28446</t>
+          <t>C28444</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's ⋮ menu opens the Add Fee/Discount dialog locked to that part</t>
+          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3451,39 +3451,39 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate.</t>
+          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-002</t>
+          <t>FD-LABOR-007</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C28447</t>
+          <t>C28445</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
+          <t>Verify the labor-line 'Add Fee/Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3493,24 +3493,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels.</t>
+          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-003</t>
+          <t>FD-PART-001</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>C28448</t>
+          <t>C28446</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
+          <t>Verify a part's ⋮ menu opens the Add Fee/Discount dialog locked to that part</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3535,24 +3535,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels.</t>
+          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-004</t>
+          <t>FD-PART-002</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C28449</t>
+          <t>C28447</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
+          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3577,24 +3577,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels.</t>
+          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-006</t>
+          <t>FD-PART-003</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>C28451</t>
+          <t>C28448</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
+          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-007</t>
+          <t>FD-PART-004</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C28452</t>
+          <t>C28449</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any fee/discount pointing to it</t>
+          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3661,24 +3661,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
+          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-008</t>
+          <t>FD-PART-006</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>C28453</t>
+          <t>C28451</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
+          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3703,39 +3703,39 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
+          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-PART-007</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>C28585</t>
+          <t>C28452</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+          <t>Verify deleting a part removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3745,39 +3745,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
+          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PART-008</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28453</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3787,24 +3787,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
+          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28585</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3829,24 +3829,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
+          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3871,24 +3871,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3913,24 +3913,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.'</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3955,24 +3955,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>C28593</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in).</t>
+          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4039,24 +4039,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds.</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PERM-009</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28593</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
+          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4081,34 +4081,34 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried.</t>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4123,39 +4123,39 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template').</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee).</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4207,39 +4207,39 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels.</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template').</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4249,34 +4249,34 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4291,34 +4291,34 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4333,39 +4333,39 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4375,39 +4375,39 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4417,39 +4417,39 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending.</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4459,39 +4459,39 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4501,34 +4501,34 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4543,24 +4543,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4585,34 +4585,34 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4627,39 +4627,39 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4669,24 +4669,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4711,34 +4711,34 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts').</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4753,34 +4753,34 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4795,34 +4795,34 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts').</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4837,39 +4837,39 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog).</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4879,34 +4879,34 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02).</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4921,39 +4921,39 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU.</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4963,34 +4963,34 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live.</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5005,34 +5005,34 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02).</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5047,34 +5047,34 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5089,34 +5089,34 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5173,34 +5173,34 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance.</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5215,39 +5215,39 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -5257,39 +5257,39 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5299,39 +5299,39 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -5341,24 +5341,24 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5383,39 +5383,39 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -5425,39 +5425,39 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -5467,39 +5467,39 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -5509,24 +5509,24 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -5551,24 +5551,24 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5593,39 +5593,39 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C28602</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -5635,39 +5635,39 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28603</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -5677,39 +5677,39 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -5719,39 +5719,39 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28605</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -5761,24 +5761,24 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-WO-001</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28424</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5803,24 +5803,24 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-WO-002</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28425</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5845,24 +5845,24 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-WO-003</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28426</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-WO-004</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28427</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5929,24 +5929,24 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-WO-006</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C28429</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -5971,24 +5971,24 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-WO-007</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28430</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -6013,24 +6013,24 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-WO-008</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28431</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -6055,24 +6055,24 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-WO-009</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28432</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6097,47 +6097,215 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>FD-WO-010</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>C28433</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-011</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>C28434</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-012</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>C28435</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-014</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>C28437</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-015</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>C28438</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass.</t>
         </is>
@@ -6275,6 +6443,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6286,7 +6458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6344,17 +6516,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-006</t>
+          <t>FD-CALC-013</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>C28573</t>
+          <t>C28580</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28573</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -6364,12 +6536,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -6379,34 +6551,34 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-008</t>
+          <t>FD-CUST-005</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>C28575</t>
+          <t>C28489</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28575</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Calculation contract</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
+          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -6421,39 +6593,39 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied.</t>
+          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-013</t>
+          <t>FD-CUST-006</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>C28580</t>
+          <t>C28490</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Calculation contract</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
+          <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6463,39 +6635,39 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied.</t>
+          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-005</t>
+          <t>FD-INLINE-003</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>C28489</t>
+          <t>C28456</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
+          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6505,39 +6677,39 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
+          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-006</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28490</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify the picker message when there are no templates left to add</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6547,34 +6719,34 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-003</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28456</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -6589,34 +6761,34 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-002</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6631,34 +6803,34 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-008</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28526</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
+          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -6673,39 +6845,39 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm).</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-009</t>
+          <t>FD-STATS-002</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
+          <t>Verify each Stats fee/discount row names its target</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6715,39 +6887,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
+          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-STATS-004</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
+          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6757,34 +6929,34 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement.</t>
+          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-001</t>
+          <t>FD-TMPL-010</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28459</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -6799,39 +6971,39 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01).</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-002</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28460</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify each Stats fee/discount row names its target</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6841,39 +7013,39 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-004</t>
+          <t>FD-WO-005</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28462</t>
+          <t>C28428</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6883,39 +7055,39 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-010</t>
+          <t>FD-WO-013</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28511</t>
+          <t>C28436</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Template admin — scoping</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
+          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6925,34 +7097,34 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned.</t>
+          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-WO-016</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C29441</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -6966,216 +7138,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>FD-VAL-001</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>C28599</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>FD-VAL-006</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>C28604</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-005</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>C28428</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-013</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-016</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>C29441</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>/No TOGGLE (not a dropdown) — corrected. DEVIATION: the §5-R15 jurisdiction note is NOT shown below the Taxable toggle in this build (checked the whole-WO Add dialog with both Flat Amount and % of Subtotal; no note present — shots wo-03/wo-05). Expected kept as the spec requirement; currently a gap.</t>
         </is>
@@ -7198,11 +7160,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8726,7 +8683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8823,9 +8780,52 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>FD-QB-014</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>C28557</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks — negative totals</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4550,27 +4550,27 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4585,24 +4585,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4627,24 +4627,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4669,39 +4669,39 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4711,24 +4711,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts').</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4837,24 +4837,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts').</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4879,39 +4879,39 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4921,34 +4921,34 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog).</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -4963,34 +4963,34 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02).</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5005,24 +5005,24 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU.</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5047,39 +5047,39 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live.</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5089,39 +5089,39 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02).</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5131,39 +5131,39 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5173,24 +5173,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -5215,24 +5215,24 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -5257,39 +5257,39 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance.</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5299,34 +5299,34 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5341,34 +5341,34 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -5383,39 +5383,39 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -5425,39 +5425,39 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -5467,39 +5467,39 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -5509,39 +5509,39 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -5551,24 +5551,24 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -5593,24 +5593,24 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -5635,24 +5635,24 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28602</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -5677,24 +5677,24 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>C28604</t>
+          <t>C28603</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5719,24 +5719,24 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -5761,39 +5761,39 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C28605</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5803,24 +5803,24 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-WO-001</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28424</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -5845,24 +5845,24 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-WO-002</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28425</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-WO-003</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28426</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -5929,24 +5929,24 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-WO-004</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28427</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5971,24 +5971,24 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-WO-006</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28429</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -6013,24 +6013,24 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-WO-007</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28430</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -6055,24 +6055,24 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-WO-008</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28431</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6097,24 +6097,24 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-WO-009</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C28432</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -6139,24 +6139,24 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-WO-010</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28433</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -6181,24 +6181,24 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-WO-011</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28434</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -6223,24 +6223,24 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-WO-012</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28435</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -6265,47 +6265,89 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>FD-WO-014</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>C28437</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-015</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>C28438</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass.</t>
         </is>
@@ -6447,6 +6489,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8683,7 +8726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8780,52 +8823,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FD-QB-014</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>C28557</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks — negative totals</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01).</t>
+          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type.</t>
+          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate).</t>
+          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01).</t>
+          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it.</t>
+          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate).</t>
+          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry.</t>
+          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate).</t>
+          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in).</t>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds.</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>/No TOGGLE (not a dropdown) — corrected. DEVIATION: the §5-R15 jurisdiction note is NOT shown below the Taxable toggle in this build (checked the whole-WO Add dialog with both Flat Amount and % of Subtotal; no note present — shots wo-03/wo-05). Expected kept as the spec requirement; currently a gap.</t>
+          <t>ll (Stories 1/2 require SFD), so the negative is only independently observable at the admin template/Processing-Fee dialog. Spec ambiguity flagged for Chris (§H.a): the change-log names 'the template dialog' as the second gated location while the §5-R15 body names the Processing Fee dialog (S8-R11).</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
+          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships.</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>org flag toggling deliberately NOT done: shared env, manual tester active today | WORDING+VIU 2026-07-13: BLOCKED-ENV: cannot take a feature-off window on the shared qb env while a manual tester is active. Wording made layman.</t>
+          <t>org flag toggling deliberately NOT done: shared env, manual tester active today | WORDING+VIU 2026-07-13: BLOCKED-ENV: cannot take a feature-off window on the shared qb env while a manual tester is active. Wording made layman. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify the work-order history still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
+          <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV + V1_2 re-VIU pending: needs a feature-off window (not takeable on the shared env) to confirm history entries stay visible. Wording made layman.</t>
+          <t>as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV + V1_2 re-VIU pending: needs a feature-off window (not takeable on the shared env) to confirm history entries stay visible. Wording made layman. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when the fee/discount screens are hidden by the feature being off</t>
+          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV: needs a feature-off window (not takeable on the shared env with a live tester).</t>
+          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV: needs a feature-off window (not takeable on the shared env with a live tester). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -459,7 +459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fees &amp; Discounts V1 — FRESH full VIU pass, 2026-07-10 (all 183 cases; V1_2 spec overlay applied 2026-07-13)</t>
+          <t>Fees &amp; Discounts V1 — FRESH full VIU pass, 2026-07-10 (all 205 cases; V1_2 spec overlay applied 2026-07-13)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
     </row>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
+          <t>10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: rate rendering reworded from 'rate badge' to plain text (item 4); calc math unchanged.</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU.</t>
+          <t>0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
+          <t>flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: step 1 whole-WO -&gt; 'Add Work Order Fee / Discount', step 2 labor line -&gt; 'Add Labor Fee / Discount' (behavior unchanged).</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried.</t>
+          <t>per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
+          <t>discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | SV-8479/8480 deconfliction 2026-07-22: 'at any scope' step reworded to the whole-WO entry label 'Add Work Order Fee / Discount' (validation is scope-independent).</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
+          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied.</t>
+          <t>10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No).</t>
+          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels.</t>
+          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels.</t>
+          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels.</t>
+          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card).</t>
+          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204).</t>
+          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried.</t>
+          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried.</t>
+          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -1862,32 +1862,32 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-016</t>
+          <t>FD-CUST-017</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C28500</t>
+          <t>C28501</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults — known bug</t>
+          <t>Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1897,39 +1897,39 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>template BOTH auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Double-add once (BUG-FD-1 not reproduced); build labels.</t>
+          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-017</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C28501</t>
+          <t>C28533</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — negative</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1939,34 +1939,34 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
+          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-001</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C28533</t>
+          <t>C28534</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1981,24 +1981,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
+          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-002</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C28534</t>
+          <t>C28535</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2023,39 +2023,39 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
+          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-003</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C28535</t>
+          <t>C28536</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2065,34 +2065,34 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
+          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-004</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C28536</t>
+          <t>C28537</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Customer document — amount format</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
+          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
+          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-005</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C28537</t>
+          <t>C28538</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2149,39 +2149,39 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
+          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-006</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>C28538</t>
+          <t>C28539</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2191,34 +2191,34 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
+          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-007</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>C28539</t>
+          <t>C28540</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2233,24 +2233,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
+          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-008</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>C28540</t>
+          <t>C28541</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2275,39 +2275,39 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
+          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-009</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>C28541</t>
+          <t>C28542</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2317,34 +2317,34 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
+          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-010</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C28542</t>
+          <t>C28543</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2359,39 +2359,39 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
+          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-011</t>
+          <t>FD-EDIT-001</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>C28543</t>
+          <t>C28476</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Customer document — layout</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
+          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2401,24 +2401,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
+          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-001</t>
+          <t>FD-EDIT-002</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>C28476</t>
+          <t>C28477</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2428,12 +2428,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
+          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2443,24 +2443,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit.</t>
+          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-002</t>
+          <t>FD-EDIT-003</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>C28477</t>
+          <t>C28478</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
+          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2485,39 +2485,39 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-003</t>
+          <t>FD-FIN-001</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>C28478</t>
+          <t>C28464</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2527,24 +2527,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
+          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-001</t>
+          <t>FD-FIN-002</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>C28464</t>
+          <t>C28465</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
+          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03).</t>
+          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-002</t>
+          <t>FD-FIN-003</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>C28465</t>
+          <t>C28466</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
+          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2611,39 +2611,39 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
+          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-003</t>
+          <t>FD-FIN-004</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C28466</t>
+          <t>C28467</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
+          <t>Verify the Work Order Fees &amp; Discounts card lists whole-work-order fees/discounts as plain text (percentage in brackets, no colored badge)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
+          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-FIN-005</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>C28467</t>
+          <t>C28468</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
+          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2695,39 +2695,39 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate.</t>
+          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-HIST-001</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C28468</t>
+          <t>C28560</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2737,34 +2737,34 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'.</t>
+          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-001</t>
+          <t>FD-HIST-002</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C28560</t>
+          <t>C28561</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2779,39 +2779,39 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-002</t>
+          <t>FD-HIST-003</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C28561</t>
+          <t>C28562</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2821,34 +2821,34 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-003</t>
+          <t>FD-HIST-005</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>C28562</t>
+          <t>C28564</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2863,39 +2863,39 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-005</t>
+          <t>FD-HIST-006</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C28564</t>
+          <t>C28565</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2905,39 +2905,39 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-006</t>
+          <t>FD-HIST-007</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C28565</t>
+          <t>C28566</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>History log — permission</t>
+          <t>Audit log — Processing Fee</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2947,39 +2947,39 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-007</t>
+          <t>FD-HIST-008</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C28566</t>
+          <t>C28567</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>History log — Processing Fee</t>
+          <t>Audit log — edit entry</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2989,39 +2989,39 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-008</t>
+          <t>FD-INLINE-001</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>C28567</t>
+          <t>C28454</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>History log — edit entry</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify a labor-line fee/discount shows inline under its line as plain text with a blank left label (no colored badge)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3031,24 +3031,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-001</t>
+          <t>FD-INLINE-002</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C28454</t>
+          <t>C28455</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify a part-line fee/discount shows inline under its part as plain text (no colored badge)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3073,24 +3073,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03).</t>
+          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-002</t>
+          <t>FD-INLINE-004</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C28455</t>
+          <t>C28457</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify the collapsed line Total adds the line's own fees and discounts (Labor + Parts + line fee/discount amounts, signed) — display only</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3115,24 +3115,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03).</t>
+          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-004</t>
+          <t>FD-INLINE-005</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C28457</t>
+          <t>C28458</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
+          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3157,39 +3157,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned.</t>
+          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-005</t>
+          <t>FD-LABOR-001</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>C28458</t>
+          <t>C28439</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
+          <t>Verify a labor line's fee/discount dialog opens locked to that line with title 'New Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3199,24 +3199,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
+          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-001</t>
+          <t>FD-LABOR-002</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C28439</t>
+          <t>C28440</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's ⋮ menu opens the Add Fee/Discount dialog locked to that labor line</t>
+          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
+          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-002</t>
+          <t>FD-LABOR-003</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C28440</t>
+          <t>C28441</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify the labor fee/discount add entry point is a three-dot menu to the left of the first technician (or 'Unassigned')</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3283,24 +3283,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
+          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: rescoped from the old per-line-row ⋮ model to the new ⋮-left-of-technician entry point + 'Add Labor Fee / Discount' (item 1). RETIRE-CANDIDATE: now overlaps kept new case FD-WO-017 (item-1 placement acceptance) — flag for user ruling.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-003</t>
+          <t>FD-LABOR-004</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C28441</t>
+          <t>C28442</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row shows its own ⋮ menu on hover</t>
+          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3325,24 +3325,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU.</t>
+          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-004</t>
+          <t>FD-LABOR-005</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C28442</t>
+          <t>C28443</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
+          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3367,24 +3367,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried.</t>
+          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-005</t>
+          <t>FD-LABOR-006</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C28443</t>
+          <t>C28444</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
+          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3409,24 +3409,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
+          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-006</t>
+          <t>FD-LABOR-007</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C28444</t>
+          <t>C28445</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
+          <t>Verify the labor-line 'Add Labor Fee / Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3451,39 +3451,39 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels.</t>
+          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-007</t>
+          <t>FD-PART-001</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C28445</t>
+          <t>C28446</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify the labor-line 'Add Fee/Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify a part's fee/discount dialog opens locked to that part with title 'New Part Fee / Discount'</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3493,24 +3493,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived.</t>
+          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-001</t>
+          <t>FD-PART-002</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>C28446</t>
+          <t>C28447</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's ⋮ menu opens the Add Fee/Discount dialog locked to that part</t>
+          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3535,24 +3535,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate.</t>
+          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-002</t>
+          <t>FD-PART-003</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C28447</t>
+          <t>C28448</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3577,24 +3577,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels.</t>
+          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-003</t>
+          <t>FD-PART-004</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>C28448</t>
+          <t>C28449</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
+          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels.</t>
+          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-004</t>
+          <t>FD-PART-006</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C28449</t>
+          <t>C28451</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
+          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3661,24 +3661,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels.</t>
+          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-006</t>
+          <t>FD-PART-007</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>C28451</t>
+          <t>C28452</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify deleting a part removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3703,24 +3703,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
+          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-007</t>
+          <t>FD-PART-008</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>C28452</t>
+          <t>C28453</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any fee/discount pointing to it</t>
+          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3745,39 +3745,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
+          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-008</t>
+          <t>FD-PCOL-001</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>C28453</t>
+          <t>C28469</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28469</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
+          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3787,34 +3787,34 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
+          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Column shows single fee/discount name+rate (Fee $6.00 / Discount -11%). Live staging (ps-scrolled).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-PCOL-002</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>C28585</t>
+          <t>C28470</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28470</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+          <t>Verify the parts-sale 'Fees &amp; Discounts' column shows values as plain text with a '+N' overflow count (no colored badge)</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3829,39 +3829,39 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PCOL-003</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28471</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28471</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify a fee-less part row adds a fee/discount from its three-dot menu 'Add Part Fee / Discount' (no '+ Add' button)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3871,34 +3871,34 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add button shown on a no-fee part. Live staging (psH2-invoiced.png); add works on editable sale via row menu. | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ 'Add Part Fee / Discount' + 'New Part Fee / Discount' title (items 13/14/18). RETIRE-CANDIDATE (F2): overlaps kept new cases FD-PSALE-002/003 — flag for user ruling.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PCOL-004</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28472</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28472</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3913,39 +3913,39 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Filled cell opens viewer with Name/Type/Calculation/Amount/Max Amount columns. Live staging (psC-viewer2rows.png).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PCOL-005</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28473</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28473</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3955,34 +3955,34 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Viewer Net adjustment = signed sum (+$12.00 + $2.00 = +$14.00). Live staging (psC-viewer2rows.png).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PCOL-006</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28474</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28474</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
+          <t>Verify a per-row Remove on the breakdown removes the fee/discount and the cell returns to its empty state (no '+ Add' button)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3997,39 +3997,39 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.'</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PCOL-007</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28475</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28475</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify the per-row three-dot 'Add Part Fee / Discount' is unavailable when the sale/work order cannot be edited</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4039,24 +4039,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add disabled on non-editable (Paid) sale. Live staging (psH2-invoiced.png, btnDisabled=true). | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ blocked-when-uneditable (item 13). RETIRE-CANDIDATE (F2): overlaps kept new case FD-PSALE-002 — flag for user ruling.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>C28593</t>
+          <t>C28585</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4081,24 +4081,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4123,24 +4123,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PERM-004</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28588</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4165,34 +4165,34 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried.</t>
+          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4207,34 +4207,34 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template').</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4249,39 +4249,39 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee).</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4291,39 +4291,39 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels.</t>
+          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4333,34 +4333,34 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PERM-009</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28593</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4375,39 +4375,39 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4417,39 +4417,39 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4459,39 +4459,39 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PERM-012</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C29922</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29922</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Fees &amp; Discounts settings page gated by settingsService (not settingsFinance)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4501,34 +4501,34 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>-confirmed equivalent behaviour this pass: Service-only user sees+manages F&amp;D; Finance-only user has no F&amp;D nav item and the route bounces to /workorders. Steps/expected mirror the automated stub (TestRail stored empty steps/expected); wording here is our reconstruction — do NOT re-push to TestRail.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-PERM-013</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C29923</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29923</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
+          <t>Service admin can complete the Fees &amp; Discounts template delete flow</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4543,34 +4543,34 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
+          <t>. Mirrored locally (id-map + this body, dev_authored) so it is tracked and not duplicated. Live-confirmed equivalent this pass: a Service-only user created and DELETED a template (confirm dialog 'Delete Template / Are you sure…'). Steps/expected mirror the automated stub; do NOT re-push to TestRail.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-PROC-001</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C28519</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Processing Fee — template builder</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4585,34 +4585,34 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
+          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-PROC-002</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28520</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Processing Fee — methods</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4627,39 +4627,39 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run.</t>
+          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-PROC-003</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28521</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4669,39 +4669,39 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU.</t>
+          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-PROC-004</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C28522</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4711,34 +4711,34 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
+          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4753,34 +4753,34 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4795,34 +4795,34 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4837,39 +4837,39 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts').</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4879,34 +4879,34 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4921,39 +4921,39 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4963,39 +4963,39 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog).</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5005,39 +5005,39 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02).</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5047,34 +5047,34 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU.</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-PSALE-001</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C29918</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5089,34 +5089,34 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live.</t>
+          <t>on label 'Add Fee / Discount' -&gt; 'Add Part Fee / Discount' (item 14) and dialog titles named ('New Part Fee / Discount' item 18; 'New Parts Sale Fee / Discount' item 19) for context; jurisdiction-note assertion unchanged. Whole-sale title/subline detail owned by kept new case FD-PSALE-008 (item 19).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5131,39 +5131,39 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02).</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5173,34 +5173,34 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5215,39 +5215,39 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -5257,39 +5257,39 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5299,39 +5299,39 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance.</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -5341,39 +5341,39 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5383,34 +5383,34 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5425,39 +5425,39 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -5467,39 +5467,39 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -5509,39 +5509,39 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -5551,34 +5551,34 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5593,39 +5593,39 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned.</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -5635,39 +5635,39 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.)</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -5677,39 +5677,39 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned.</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -5719,34 +5719,34 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU.</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>C28604</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -5761,39 +5761,39 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5803,39 +5803,39 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU.</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5845,39 +5845,39 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped).</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5887,39 +5887,39 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message').</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5929,39 +5929,39 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10).</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5971,34 +5971,34 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)').</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -6013,39 +6013,39 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live).</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -6055,39 +6055,39 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -6097,39 +6097,39 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.)</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -6139,34 +6139,34 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-TMPL-018</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C29917</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — jurisdiction note</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -6181,34 +6181,34 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>s' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -6223,34 +6223,34 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total').</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -6265,34 +6265,34 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05).</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -6307,49 +6307,805 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03).</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>FD-VAL-004</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>C28602</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-005</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>C28603</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-006</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>C28604</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-007</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>C28605</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-001</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>C28424</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-002</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>C28425</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-003</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>C28426</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-004</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>C28427</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-005</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>C28428</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-006</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>C28429</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-007</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>C28430</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-008</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>C28431</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-009</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>C28432</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-010</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>C28433</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-011</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>C28434</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-012</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>C28435</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-014</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>C28437</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-015</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>C28438</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C153" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass.</t>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-016</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>C29441</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>as no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
         </is>
       </c>
     </row>
@@ -6490,725 +7246,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="90" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>FD ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>TestRail Case ID</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>TestRail Link</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Fresh Status (2026-07-10)</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Fresh Evidence / Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FD-CALC-013</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>C28580</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FD-CUST-005</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>C28489</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FD-CUST-006</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>C28490</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify the picker message when there are no templates left to add</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FD-INLINE-003</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>C28456</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Inline display (Lines tab)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FD-PERM-002</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>C28586</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FD-PROC-008</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>C28526</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — WO behavior</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FD-PROC-009</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>C28527</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — calculation</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FD-STATS-001</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>C28459</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Statistics tab</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FD-STATS-002</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>C28460</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Statistics tab</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify each Stats fee/discount row names its target</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>FD-STATS-004</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>C28462</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Statistics tab</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-010</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>C28511</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — scoping</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>FD-VAL-001</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>C28599</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-005</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C28428</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-013</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-016</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>C29441</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>ll (Stories 1/2 require SFD), so the negative is only independently observable at the admin template/Processing-Fee dialog. Spec ambiguity flagged for Chris (§H.a): the change-log names 'the template dialog' as the second gated location while the §5-R15 body names the Processing Fee dialog (S8-R11).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7272,27 +7333,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-001</t>
+          <t>FD-CALC-013</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>C28469</t>
+          <t>C28580</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -7302,123 +7363,123 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-002</t>
+          <t>FD-CUST-005</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>C28470</t>
+          <t>C28489</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has several fees/discounts</t>
+          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
+          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-003</t>
+          <t>FD-CUST-006</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>C28471</t>
+          <t>C28490</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no fees/discounts</t>
+          <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
+          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-004</t>
+          <t>FD-INLINE-003</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>C28472</t>
+          <t>C28456</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
+          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7428,81 +7489,81 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
+          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-005</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28473</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-006</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28474</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify a per-row Remove on the breakdown removes the fee/discount and closes when the last one is removed</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7512,81 +7573,81 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-007</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28475</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify the '+ Add' button is disabled when the sale/work order cannot be edited</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-004</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28588</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
+          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7596,180 +7657,180 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate.</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-001</t>
+          <t>FD-STATS-002</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28519</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template builder</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
+          <t>Verify each Stats fee/discount row names its target</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
+          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-002</t>
+          <t>FD-STATS-004</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28520</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — methods</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
+          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
+          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-003</t>
+          <t>FD-TMPL-010</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28521</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no Max Amount</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships.</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-004</t>
+          <t>FD-WO-013</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28522</t>
+          <t>C28436</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — taxable + jurisdiction note</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
+          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>VIU-Blocked-NotBuilt</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships.</t>
+          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged.</t>
         </is>
       </c>
     </row>
@@ -7788,6 +7849,72 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
   </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FD ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>TestRail Case ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>TestRail Link</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Fresh Status (2026-07-10)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Fresh Evidence / Note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8039,7 +8166,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -8689,7 +8816,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance.</t>
+          <t>empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8784,48 +8911,732 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>FD-CALC-018</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify a work order line total adds the line's own fees to Labor and Parts (Labor $250 + fee +$50.00 + Part $20.00 + fee +$2.20 → line total $322.20)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>scounts (showed $270.00). Fixed backend (Stefan Vukovic, PR ShopView/shopview#2228) to add the line's signed fee/discount amounts on top per spec S3-R18. Display-only, no stored values change. QA Passed on staging 2026-07-22. Concrete worked example from the ticket ($322.20) used as expected values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-019</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify a discount on a line subtracts from the line total while a fee adds (fees add, discounts subtract in the line total)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 / S3-R18: the line total rolls in the line's SIGNED fee/discount amounts (fees add, discounts subtract). Complements FD-CALC-018 (all-fees case) by proving a discount subtracts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-020</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify a line with no fees or discounts shows a line total of Labor + Parts only (unchanged by the fix)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 QA step 2 / S3-R18: a line without any fee/discount keeps a gross Labor + Parts total (no change from the fix).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-021</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Estimate document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Estimate document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-022</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Invoice document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Invoice document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-023</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify that when the Fees &amp; Discounts feature is turned off, the line total is Labor + Parts only (gross), with no fee/discount rolled in</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 QA step 4 / S3-R18: for an organization without the Fees &amp; Discounts feature, line totals stay gross-only (the roll-in is gated by the feature).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-024</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify the backend per-line total includes the line's signed fee/discount amounts (Labor $250 + $50.00 + Part $20.00 + $2.20 → total_cost 322.20)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>R18: backend fix in the per-line total_cost computation (Stefan Vukovic, PR ShopView/shopview#2228) — previously Labor + Parts gross only, now adds the line's signed fee/discount amounts. Display-only, no stored values change. API-section case per Standing Rule 4 (verifies a backend value/response).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>FD-PART-005</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>C28450</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order | WORDING+VIU 2026-07-13: BLOCKED/PENDING: requested→received transition blocked by the env-wide WO line-create 500 + completed-line part-request lock — cannot drive the transition. Build labels applied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FD-PSALE-002</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>QA passed on staging 2026-07-22 (✅).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FD-PSALE-003</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>QA passed on staging 2026-07-22 (✅).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FD-PSALE-004</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Parts Sale — Fees &amp; Discounts card</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Same convention as work-order card item 5. QA passed on staging 2026-07-22 (✅).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FD-PSALE-006</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Parts Sale — Financial Info card</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Matches work-order Financial Info card (item 7). Green mockup omits the amount; the amount is existing behavior. QA passed on staging 2026-07-22 (✅).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FD-PSALE-008</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Part Sale — Fee/Discount dialog</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>top-right three-dot entry label 'Add Parts Sale Fee / Discount' is taken from the item-19 description text; VIU-confirm the exact menu label, its placement in the top-right three-dot menu, and the dialog title/subline LIVE. QA marked item 19 passed on staging 2026-07-22 (✅) but on a duplicate image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FD-PSALE-009</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Parts Sale — Statistics tab</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>No PO before/after picture for item 20 — it mirrors work-order item 12. QA passed on staging 2026-07-22 (✅, image 58876). VIU-confirm the exact Statistics-tab heading labels live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-017</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Labor-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>iscount' is correct (✅) but found the three-dot menu rendered to the RIGHT of 'Unassigned'; the fix must move it to the LEFT of 'Unassigned' (image 58861 red annotation 'Move it to left of unassigned'). Green target = Picture 1 (58831). VIU-Pending: verify the LEFT placement live once the fix lands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-018</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>QA passed this item on staging 2026-07-22 (✅). Menu label corrected from 'Add Fee / Discount' to 'Add Part Fee / Discount'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-021</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Copy updated to '…after all other fees &amp; discounts.' and ensured it renders. Picture 7 is a mockup. QA passed on staging 2026-07-22 (✅).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-025</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Label-only change; menu order unchanged. QA passed on staging 2026-07-22 (✅).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-028</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify the tax-jurisdiction note and the 'Pass convenience fee to customer' banner still appear after the fee/discount UI updates</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Regression check per SV-8479 NOTES — these UI corrections must not remove the jurisdiction tax note or the convenience-fee banner. VIU-confirm live.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-10.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: rate rendering reworded from 'rate badge' to plain text (item 4); calc math unchanged.</t>
+          <t>10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: rate rendering reworded from 'rate badge' to plain text (item 4); calc math unchanged. | VIU 2026-07-22 LIVE: base×percent calc confirmed (20% of $509.90 labor = +$101.98; plain text, no badge). WORDING CORRECTED '+10%' -&gt; '10%' — inline percentage FEE renders bare with no leading '+' (matches live build + batch-1 FD-CALC-018/019 fix). Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: step 1 whole-WO -&gt; 'Add Work Order Fee / Discount', step 2 labor line -&gt; 'Add Labor Fee / Discount' (behavior unchanged).</t>
+          <t>flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: step 1 whole-WO -&gt; 'Add Work Order Fee / Discount', step 2 labor line -&gt; 'Add Labor Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Work Order Fee / Discount' (step 1) and 'Add Labor Fee / Discount' (step 2) both confirmed present; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png, wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
+          <t>per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | SV-8479/8480 deconfliction 2026-07-22: 'at any scope' step reworded to the whole-WO entry label 'Add Work Order Fee / Discount' (validation is scope-independent).</t>
+          <t>discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | SV-8479/8480 deconfliction 2026-07-22: 'at any scope' step reworded to the whole-WO entry label 'Add Work Order Fee / Discount' (validation is scope-independent). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -1309,34 +1309,30 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-001</t>
+          <t>FD-CALC-018</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28485</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
+          <t>Verify a work order line total adds the line's own fees to Labor and Parts (Labor $250 + fee +$50.00 + Part $20.00 + fee +$2.20 → line total $322.20)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1349,36 +1345,31 @@
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
-        </is>
+      <c r="H17" s="2">
+        <f> $392.40 = 290 + labor fee ttt +20% ($58.00) + 40 + part fee test +11% ($4.40); NOT gross $330. Rows render PLAIN TEXT bare '20%'/'11%' (no plus sign, no colored badge; HTML span text-grey-7). Ev: 018-lines-collapsed-full.png, 018-lines-expanded-full.png, api-FD-CALC-018-024-total_cost-392.40.json.</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-002</t>
+          <t>FD-CALC-019</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28486</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
+          <t>Verify a discount on a line subtracts from the line total while a fee adds (fees add, discounts subtract in the line total)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1393,39 +1384,35 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
+          <t>acted -&gt; collapsed line Total = $384.00 = 290 + 58 + 40 - 4.00 (fee adds, discount subtracts). Discount rate renders '-10%' (en-dash minus) plain text, resolved -$4.00; fee rate renders bare '20%'. Ev: 019-lines-collapsed-full.png, 019-lines-expanded-full.png, api-FD-CALC-019-total_cost-384.00.json.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-003</t>
+          <t>FD-CALC-020</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28487</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a single template as a customer default via the picker</t>
+          <t>Verify a line with no fees or discounts shows a line total of Labor + Parts only (unchanged by the fix)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1435,34 +1422,30 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
+          <t>tal (no change from the fix). | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. A ZZAUTOTEST line with no fees/discounts (Labor $290 + Parts $40) shows collapsed line Total = $330.00 = gross Labor + Parts only, no Fees/Discounts rows. Ev: 020-lines-nofee-line.png, api-baseline-nofees-total_cost-330.json.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-004</t>
+          <t>FD-CALC-021</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C28488</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
+          <t>Verify the Estimate document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1477,39 +1460,35 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
+          <t>0'; the document Line Total = $330.00 (gross Labor+Parts, fee NOT folded in); every fee/discount (incl. line-level ttt +$58.00 and pdisc ($4.00)) listed once in the Fees &amp; Discounts breakdown -&gt; no double-count. Confirms the fix is Lines-tab display-only; estimate unchanged. Ev: 021-finance-tab.png.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-007</t>
+          <t>FD-CALC-022</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C28491</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default from the row needs no confirmation</t>
+          <t>Verify the Invoice document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1519,39 +1498,35 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
+          <t>Invoice document (Finance tab toggle, INV-S3-25836): renders identically to the estimate — Labor gross $290.00, the line fee prints as its own row '↳ ttt (% of labor) $58.00', document Line Total = $330.00 (gross, fee not folded in), each fee listed once -&gt; no double-count. Ev: 022-invoice-view.png.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-008</t>
+          <t>FD-CALC-024</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C28492</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
+          <t>Verify the backend per-line total includes the line's signed fee/discount amounts (Labor $250 + $50.00 + Part $20.00 + $2.20 → total_cost 322.20)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1561,34 +1536,34 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
+          <t>Stored line amounts unchanged (labour_rate 145, total_labour_cost 290, part sell_price 40); the fee/discount amounts live separately under line.adjustments[] and part_requests[].adjustments[] (resolvedAmount 58 / 4.40) — computed total is display-only. Ev: api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-009</t>
+          <t>FD-CUST-001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C28493</t>
+          <t>C28485</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
+          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1603,39 +1578,39 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-010</t>
+          <t>FD-CUST-002</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C28494</t>
+          <t>C28486</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
+          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1645,34 +1620,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
+          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-011</t>
+          <t>FD-CUST-003</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C28495</t>
+          <t>C28487</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
+          <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1687,39 +1662,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-012</t>
+          <t>FD-CUST-004</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>C28496</t>
+          <t>C28488</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
+          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1729,39 +1704,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-013</t>
+          <t>FD-CUST-007</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C28497</t>
+          <t>C28491</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a customer removes that customer's default links</t>
+          <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1771,39 +1746,39 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-014</t>
+          <t>FD-CUST-008</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C28498</t>
+          <t>C28492</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults seeding</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
+          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1813,34 +1788,34 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
+          <t>empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-015</t>
+          <t>FD-CUST-009</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C28499</t>
+          <t>C28493</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — permissions</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
+          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1855,39 +1830,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
+          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-017</t>
+          <t>FD-CUST-010</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C28501</t>
+          <t>C28494</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — negative</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1897,34 +1872,34 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
+          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-001</t>
+          <t>FD-CUST-011</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C28533</t>
+          <t>C28495</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1939,34 +1914,34 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
+          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-002</t>
+          <t>FD-CUST-012</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C28534</t>
+          <t>C28496</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
+          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1981,39 +1956,39 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
+          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-003</t>
+          <t>FD-CUST-013</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C28535</t>
+          <t>C28497</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2023,39 +1998,39 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
+          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-004</t>
+          <t>FD-CUST-014</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C28536</t>
+          <t>C28498</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Customer document — amount format</t>
+          <t>Customer defaults seeding</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
+          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2065,34 +2040,34 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
+          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-005</t>
+          <t>FD-CUST-015</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C28537</t>
+          <t>C28499</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
+          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2107,39 +2082,39 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
+          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-006</t>
+          <t>FD-CUST-017</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C28538</t>
+          <t>C28501</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2149,39 +2124,39 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
+          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-007</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>C28539</t>
+          <t>C28533</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2191,39 +2166,39 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
+          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-008</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>C28540</t>
+          <t>C28534</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2233,39 +2208,39 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
+          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-009</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>C28541</t>
+          <t>C28535</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2275,39 +2250,39 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
+          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-010</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>C28542</t>
+          <t>C28536</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2317,39 +2292,39 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
+          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-011</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C28543</t>
+          <t>C28537</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Customer document — layout</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
+          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2359,34 +2334,34 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
+          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-001</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>C28476</t>
+          <t>C28538</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2401,34 +2376,34 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-002</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>C28477</t>
+          <t>C28539</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2443,34 +2418,34 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-003</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>C28478</t>
+          <t>C28540</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2485,39 +2460,39 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
+          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-001</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>C28464</t>
+          <t>C28541</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal</t>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2527,34 +2502,34 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change).</t>
+          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-002</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>C28465</t>
+          <t>C28542</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2569,34 +2544,34 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
+          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-003</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>C28466</t>
+          <t>C28543</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2611,34 +2586,34 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
+          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-EDIT-001</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C28467</t>
+          <t>C28476</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify the Work Order Fees &amp; Discounts card lists whole-work-order fees/discounts as plain text (percentage in brackets, no colored badge)</t>
+          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2653,34 +2628,34 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication.</t>
+          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-EDIT-002</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>C28468</t>
+          <t>C28477</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
+          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2695,39 +2670,39 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-001</t>
+          <t>FD-EDIT-003</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C28560</t>
+          <t>C28478</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Audit log</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2737,34 +2712,34 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-002</t>
+          <t>FD-FIN-001</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C28561</t>
+          <t>C28464</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Audit log</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2779,34 +2754,34 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change). | VIU 2026-07-22 LIVE: Financial Info order = Parts $40.00, Labor $509.90, Shop Supplies $53.54, Fees &amp; Discounts (10) $273.31, Subtotal $876.75, GST, Total, Balance — F&amp;D line renders directly above Subtotal. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-003</t>
+          <t>FD-FIN-002</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C28562</t>
+          <t>C28465</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Audit log</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
+          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2821,34 +2796,34 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-005</t>
+          <t>FD-FIN-003</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>C28564</t>
+          <t>C28466</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Audit log — visibility</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2863,34 +2838,34 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-006</t>
+          <t>FD-FIN-004</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C28565</t>
+          <t>C28467</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Audit log — permission</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
+          <t>Verify the Work Order Fees &amp; Discounts card lists whole-work-order fees/discounts as plain text (percentage in brackets, no colored badge)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2905,34 +2880,34 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication. | VIU 2026-07-22 LIVE: card titled 'Work Order Fees &amp; Discounts', lists only whole-WO entries as plain text with bracketed percent — fee 'Customer Fee (10%) +$65.88', discount 'WO Disc (−5%) −$32.94', flat 'Flat Fee 2 +$32.00'/'Flat Fee +$11.00' (name+amount, no brackets); each entry has a ⋮ menu; card renders above Financial Info. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-007</t>
+          <t>FD-FIN-005</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C28566</t>
+          <t>C28468</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Audit log — Processing Fee</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
+          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2947,39 +2922,39 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-008</t>
+          <t>FD-HIST-001</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C28567</t>
+          <t>C28560</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Audit log — edit entry</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2989,34 +2964,34 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-001</t>
+          <t>FD-HIST-002</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>C28454</t>
+          <t>C28561</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount shows inline under its line as plain text with a blank left label (no colored badge)</t>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3031,39 +3006,39 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half).</t>
+          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-002</t>
+          <t>FD-HIST-003</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C28455</t>
+          <t>C28562</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount shows inline under its part as plain text (no colored badge)</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3073,34 +3048,34 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half).</t>
+          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-004</t>
+          <t>FD-HIST-005</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C28457</t>
+          <t>C28564</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify the collapsed line Total adds the line's own fees and discounts (Labor + Parts + line fee/discount amounts, signed) — display only</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3115,39 +3090,39 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU.</t>
+          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-005</t>
+          <t>FD-HIST-006</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C28458</t>
+          <t>C28565</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3157,39 +3132,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
+          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-001</t>
+          <t>FD-HIST-007</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>C28439</t>
+          <t>C28566</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Audit log — Processing Fee</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's fee/discount dialog opens locked to that line with title 'New Labor Fee / Discount'</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3199,39 +3174,39 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023.</t>
+          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-002</t>
+          <t>FD-HIST-008</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C28440</t>
+          <t>C28567</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Audit log — edit entry</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3241,39 +3216,39 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged).</t>
+          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-003</t>
+          <t>FD-INLINE-001</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C28441</t>
+          <t>C28454</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify the labor fee/discount add entry point is a three-dot menu to the left of the first technician (or 'Unassigned')</t>
+          <t>Verify a labor-line fee/discount shows inline under its line as plain text with a blank left label (no colored badge)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3283,39 +3258,39 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: rescoped from the old per-line-row ⋮ model to the new ⋮-left-of-technician entry point + 'Add Labor Fee / Discount' (item 1). RETIRE-CANDIDATE: now overlaps kept new case FD-WO-017 (item-1 placement acceptance) — flag for user ruling.</t>
+          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half). | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): sign convention RE-VERIFIED live on the Lines tab — a percentage labor FEE renders as a BARE '20%' (no sign) in plain grey text (HTML span text-grey-7, no colored badge/pill); a percentage DISCOUNT renders '−10%' (en-dash minus); resolved amount is signed on the right ('+$58.00' / '−$4.00'); '↳' arrow, blank left label. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Labor Fee 20%' (fee bare %, blank left label, plain text, no badge) '+$101.98'; '↳ Labor Disc −10% −$50.99' (discount minus). Ev: wo/inline-expanded-text.txt, wo/inline-expanded.png.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-004</t>
+          <t>FD-INLINE-002</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C28442</t>
+          <t>C28455</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
+          <t>Verify a part-line fee/discount shows inline under its part as plain text (no colored badge)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3325,34 +3300,34 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged).</t>
+          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half). | LIVE STAGING VIU 2026-07-22: part-line sign convention RE-VERIFIED live — a percentage part FEE renders bare '11%' (no sign) plain grey text (no badge); a percentage part DISCOUNT renders '−10%' (en-dash minus); resolved signed '+$4.40' / '−$4.00'. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Part Fee 11% +$4.40' plain text, no badge. Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-005</t>
+          <t>FD-INLINE-004</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C28443</t>
+          <t>C28457</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
+          <t>Verify the collapsed line Total adds the line's own fees and discounts (Labor + Parts + line fee/discount amounts, signed) — display only</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3367,34 +3342,34 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
+          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU. | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): RE-CONFIRMED live — the collapsed line Total on the Lines tab adds the line's own SIGNED fee/discount amounts on top of gross Labor + Parts: $392.40 with a labor fee +20% ($58.00) + part fee +11% ($4.40) on a $290 labor / $40 parts line; $330.00 gross when the line has no fees; display-only, no stored value changes. Ev: 018-lines-collapsed-full.png, 020-lines-nofee-line.png, api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-006</t>
+          <t>FD-INLINE-005</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C28444</t>
+          <t>C28458</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
+          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3409,24 +3384,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-007</t>
+          <t>FD-LABOR-001</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C28445</t>
+          <t>C28439</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3436,12 +3411,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify the labor-line 'Add Labor Fee / Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify a labor line's fee/discount dialog opens locked to that line with title 'New Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3451,39 +3426,39 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged.</t>
+          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023. | VIU 2026-07-22 LIVE: labor dialog title 'New Labor Fee / Discount', subline 'Applying To: Line 1 Labor — ZZAUTOTEST 8480 line', scope locked. Ev: wo/FD-LABOR-001-labor-dialog.png, wo/labor-dialog-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-001</t>
+          <t>FD-LABOR-002</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C28446</t>
+          <t>C28440</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's fee/discount dialog opens locked to that part with title 'New Part Fee / Discount'</t>
+          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3493,39 +3468,39 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024.</t>
+          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-002</t>
+          <t>FD-LABOR-004</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>C28447</t>
+          <t>C28442</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
+          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3535,39 +3510,39 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged.</t>
+          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-003</t>
+          <t>FD-LABOR-005</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C28448</t>
+          <t>C28443</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
+          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3577,39 +3552,39 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
+          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-004</t>
+          <t>FD-LABOR-006</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>C28449</t>
+          <t>C28444</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
+          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3619,34 +3594,34 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
+          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-006</t>
+          <t>FD-LABOR-007</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C28451</t>
+          <t>C28445</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify the labor-line 'Add Labor Fee / Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3661,24 +3636,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
+          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged. | VIU 2026-07-22 LIVE: menu label 'Add Labor Fee / Discount' confirmed present; permission-negative behavior (hidden without Work Order Lines: Create &amp; Edit) unchanged from prior verification — role-negative not re-driven this UI batch.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-007</t>
+          <t>FD-PART-001</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>C28452</t>
+          <t>C28446</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3688,12 +3663,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any fee/discount pointing to it</t>
+          <t>Verify a part's fee/discount dialog opens locked to that part with title 'New Part Fee / Discount'</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3703,24 +3678,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
+          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024. | VIU 2026-07-22 LIVE: part menu label 'Add Part Fee / Discount' + dialog title 'New Part Fee / Discount', subline 'Applying To: Line 1 Part — Turbocharger Oil', default Calculation Type '% Of Parts Total'. Ev: wo/FD-PART-001-part-dialog.png, wo/part-dialog-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-008</t>
+          <t>FD-PART-002</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>C28453</t>
+          <t>C28447</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3730,12 +3705,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
+          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3745,34 +3720,34 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
+          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged. | VIU 2026-07-22 LIVE: inline part fee renders plain text ('Part Fee 11% +$4.40'), no colored badge; per-item flat calc unchanged (verified prior passes). Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-001</t>
+          <t>FD-PART-003</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>C28469</t>
+          <t>C28448</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3787,34 +3762,34 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Column shows single fee/discount name+rate (Fee $6.00 / Discount -11%). Live staging (ps-scrolled).</t>
+          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-002</t>
+          <t>FD-PART-004</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>C28470</t>
+          <t>C28449</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale 'Fees &amp; Discounts' column shows values as plain text with a '+N' overflow count (no colored badge)</t>
+          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3829,34 +3804,34 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.)</t>
+          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-003</t>
+          <t>FD-PART-006</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C28471</t>
+          <t>C28451</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee-less part row adds a fee/discount from its three-dot menu 'Add Part Fee / Discount' (no '+ Add' button)</t>
+          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3871,39 +3846,39 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add button shown on a no-fee part. Live staging (psH2-invoiced.png); add works on editable sale via row menu. | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ 'Add Part Fee / Discount' + 'New Part Fee / Discount' title (items 13/14/18). RETIRE-CANDIDATE (F2): overlaps kept new cases FD-PSALE-002/003 — flag for user ruling.</t>
+          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-004</t>
+          <t>FD-PART-007</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>C28472</t>
+          <t>C28452</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
+          <t>Verify deleting a part removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3913,34 +3888,34 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Filled cell opens viewer with Name/Type/Calculation/Amount/Max Amount columns. Live staging (psC-viewer2rows.png).</t>
+          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-005</t>
+          <t>FD-PART-008</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>C28473</t>
+          <t>C28453</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
+          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3955,34 +3930,34 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Viewer Net adjustment = signed sum (+$12.00 + $2.00 = +$14.00). Live staging (psC-viewer2rows.png).</t>
+          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-006</t>
+          <t>FD-PCOL-001</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>C28474</t>
+          <t>C28469</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28469</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify a per-row Remove on the breakdown removes the fee/discount and the cell returns to its empty state (no '+ Add' button)</t>
+          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3997,24 +3972,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13).</t>
+          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Column shows single fee/discount name+rate (Fee $6.00 / Discount -11%). Live staging (ps-scrolled).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-007</t>
+          <t>FD-PCOL-002</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>C28475</t>
+          <t>C28470</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28470</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4024,12 +3999,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-row three-dot 'Add Part Fee / Discount' is unavailable when the sale/work order cannot be edited</t>
+          <t>Verify the parts-sale 'Fees &amp; Discounts' column shows values as plain text with a '+N' overflow count (no colored badge)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4039,39 +4014,39 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add disabled on non-editable (Paid) sale. Live staging (psH2-invoiced.png, btnDisabled=true). | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ blocked-when-uneditable (item 13). RETIRE-CANDIDATE (F2): overlaps kept new case FD-PSALE-002 — flag for user ruling.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.) | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: NEXUS cell = 'Part Fee 11% +1' plain text, no badge, fee no sign.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-PCOL-003</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>C28585</t>
+          <t>C28471</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28471</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+          <t>Verify a fee-less part row adds a fee/discount from its three-dot menu 'Add Part Fee / Discount' (no '+ Add' button)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4081,34 +4056,34 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add button shown on a no-fee part. Live staging (psH2-invoiced.png); add works on editable sale via row menu. | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ 'Add Part Fee / Discount' + 'New Part Fee / Discount' title (items 13/14/18). RETIRE-CANDIDATE (F2): overlaps kept new cases FD-PSALE-002/003 — flag for user ruling. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: fee-less row no '+ Add'; ⋮ 'Add Part Fee / Discount' -&gt; dialog 'New Part Fee / Discount'.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PCOL-004</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28472</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28472</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4123,39 +4098,39 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Filled cell opens viewer with Name/Type/Calculation/Amount/Max Amount columns. Live staging (psC-viewer2rows.png).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-004</t>
+          <t>FD-PCOL-005</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>C28588</t>
+          <t>C28473</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28473</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
+          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4165,34 +4140,34 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Viewer Net adjustment = signed sum (+$12.00 + $2.00 = +$14.00). Live staging (psC-viewer2rows.png).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PCOL-006</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28474</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28474</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify a per-row Remove on the breakdown removes the fee/discount and the cell returns to its empty state (no '+ Add' button)</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4207,39 +4182,39 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: breakdown viewer per-row delete -&gt; confirm 'Remove Fee / Discount' -&gt; removed -&gt; empty state, no '+ Add'.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PCOL-007</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28475</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28475</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify the per-row three-dot 'Add Part Fee / Discount' is unavailable when the sale/work order cannot be edited</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4249,24 +4224,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add disabled on non-editable (Paid) sale. Live staging (psH2-invoiced.png, btnDisabled=true). | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ blocked-when-uneditable (item 13). RETIRE-CANDIDATE (F2): overlaps kept new case FD-PSALE-002 — flag for user ruling. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: Paid sale P3-1088 (editable=false) has NO '+ Add' and NO per-row ⋮ menu (button_part_request_menu_* count 0) -&gt; add unavailable/blocked when non-editable.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28585</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4276,7 +4251,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4291,24 +4266,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4318,7 +4293,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4333,24 +4308,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PERM-004</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28593</t>
+          <t>C28588</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4360,12 +4335,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4375,24 +4350,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4402,7 +4377,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4417,24 +4392,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4444,12 +4419,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4459,24 +4434,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-012</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C29922</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29922</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4486,7 +4461,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Fees &amp; Discounts settings page gated by settingsService (not settingsFinance)</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4501,24 +4476,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>-confirmed equivalent behaviour this pass: Service-only user sees+manages F&amp;D; Finance-only user has no F&amp;D nav item and the route bounces to /workorders. Steps/expected mirror the automated stub (TestRail stored empty steps/expected); wording here is our reconstruction — do NOT re-push to TestRail.</t>
+          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-013</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C29923</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29923</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4528,7 +4503,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Service admin can complete the Fees &amp; Discounts template delete flow</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4543,39 +4518,39 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>. Mirrored locally (id-map + this body, dev_authored) so it is tracked and not duplicated. Live-confirmed equivalent this pass: a Service-only user created and DELETED a template (confirm dialog 'Delete Template / Are you sure…'). Steps/expected mirror the automated stub; do NOT re-push to TestRail.</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-001</t>
+          <t>FD-PERM-009</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28519</t>
+          <t>C28593</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template builder</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4585,34 +4560,34 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-002</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28520</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — methods</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4627,34 +4602,34 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-003</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28521</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no Max Amount</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4669,34 +4644,34 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-004</t>
+          <t>FD-PERM-012</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28522</t>
+          <t>C29922</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29922</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — taxable + jurisdiction note</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
+          <t>Fees &amp; Discounts settings page gated by settingsService (not settingsFinance)</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4711,34 +4686,34 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PERM-013</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C29923</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29923</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Service admin can complete the Fees &amp; Discounts template delete flow</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4753,34 +4728,34 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PROC-001</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28519</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — template builder</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4795,39 +4770,39 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PROC-002</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28520</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Processing Fee — methods</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4837,34 +4812,34 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PROC-003</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28521</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4879,39 +4854,39 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
+          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PROC-004</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28522</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4921,39 +4896,39 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
+          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4963,39 +4938,39 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5005,39 +4980,39 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5047,34 +5022,34 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-001</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C29918</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Part Sale — Fee/Discount dialog</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5089,39 +5064,39 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>on label 'Add Fee / Discount' -&gt; 'Add Part Fee / Discount' (item 14) and dialog titles named ('New Part Fee / Discount' item 18; 'New Parts Sale Fee / Discount' item 19) for context; jurisdiction-note assertion unchanged. Whole-sale title/subline detail owned by kept new case FD-PSALE-008 (item 19).</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5131,39 +5106,39 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5173,39 +5148,39 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -5215,39 +5190,39 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -5257,34 +5232,34 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-PSALE-001</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C29918</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5299,39 +5274,35 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-PSALE-002</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
+          <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -5341,39 +5312,35 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
+          <t xml:space="preserve"> NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. F&amp;D column has no '+ Add' (grep '+Add'=0); per-row ⋮ 'Add Part Fee / Discount' + top-right ⋮ 'Add Parts Sale Fee / Discount' both present.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-PSALE-003</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
+          <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5383,34 +5350,30 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
+          <t>TEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Per-part ⋮ menu text = 'Add Part Fee / Discount' exactly; opens 'New Part Fee / Discount' dialog.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-PSALE-004</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Parts Sale — Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5425,39 +5388,35 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Whole-sale card 'Parts Sale Fees &amp; Discounts' live: 'Customer Fee (10%) +$82.12', 'Sale Disc (−5%) −$41.06', 'Flat Fee +$50.00' (flat name-only), 'Processing Fee (6%) +$51.73' — plain text, no badge, bracket %/sign convention matches WO card item 5.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-PSALE-006</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr"/>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Parts Sale — Financial Info card</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
+          <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -5467,34 +5426,30 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
+          <t>ded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: 'Fees &amp; Discounts (6) $189.27' directly above Subtotal $963.95 in Financial Info.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-PSALE-008</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
+          <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5509,39 +5464,35 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
+          <t>). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. VIU-CONFIRM RESOLVED (Picture 26 was missing): top-right ⋮ label CONFIRMED LIVE = 'Add Parts Sale Fee / Discount'; dialog title 'New Parts Sale Fee / Discount'; subline 'Applying To: Entire Parts Sale'. Case wording already matched.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-PSALE-009</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr"/>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Parts Sale — Statistics tab</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
+          <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -5551,34 +5502,34 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>ss rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Statistics F&amp;D (6) section live headings '% Amount'; flat fee blank %; rows +11%/+6%/+10% fees + −5% discounts; 'Total +$189.27'.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5593,34 +5544,34 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -5635,39 +5586,39 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -5677,34 +5628,34 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5719,34 +5670,34 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -5761,34 +5712,34 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -5803,39 +5754,39 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5845,39 +5796,39 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5887,39 +5838,39 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
+          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5929,39 +5880,39 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU. | VIU 2026-07-22 LIVE: prior 'no headers' deviation RESOLVED — Stats tab 'Fees &amp; Discounts (10)' section now shows the '% Amount' column headings. Rows show percent under % (blank for flat: 'Flat Fee 2 +$32.00', 'Flat Fee +$11.00') and signed amount under Amount ('Labor Fee +20% +$101.98', 'Labor Disc −10% −$50.99', 'Customer Fee +10% +$65.88', 'WO Disc −5% −$32.94'), with 'Total +$273.31'. Ev: wo/FD-STATS-001-stats-tab.png, wo/stats-bodytext.txt.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5971,34 +5922,34 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -6013,39 +5964,39 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -6055,34 +6006,34 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6097,39 +6048,39 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -6139,34 +6090,34 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-018</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>C29917</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Template admin — jurisdiction note</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -6181,34 +6132,34 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>s' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-001</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>C28599</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
+          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -6223,39 +6174,39 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -6265,39 +6216,39 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -6307,39 +6258,39 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -6349,39 +6300,39 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -6391,34 +6342,34 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>C28604</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -6433,34 +6384,34 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -6475,39 +6426,39 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -6517,39 +6468,39 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026.</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -6559,34 +6510,34 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -6601,39 +6552,39 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -6643,39 +6594,39 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-005</t>
+          <t>FD-TMPL-018</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>C28428</t>
+          <t>C29917</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — jurisdiction note</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -6685,39 +6636,39 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -6727,39 +6678,39 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -6769,34 +6720,34 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -6811,39 +6762,39 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28602</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -6853,34 +6804,34 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C28603</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6895,39 +6846,39 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6937,39 +6888,39 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28605</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -6979,24 +6930,24 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-WO-001</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28424</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -7006,12 +6957,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -7021,24 +6972,24 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026. | VIU 2026-07-22 LIVE: whole-WO dialog opens from toolbar menu; title 'New Work Order Fee / Discount', subline 'Applying To: Entire Work Order', no scope dropdown. Ev: wo/FD-WO-001-wo-dialog.png, wo/wo-dialog-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-015</t>
+          <t>FD-WO-002</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>C28438</t>
+          <t>C28425</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -7048,12 +6999,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -7063,49 +7014,705 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>FD-WO-003</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>C28426</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-004</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>C28427</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-005</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>C28428</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-006</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>C28429</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-007</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>C28430</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-008</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>C28431</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-009</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>C28432</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-010</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>C28433</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-011</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>C28434</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-012</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>C28435</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-014</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>C28437</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-015</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>C28438</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-016</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>C29441</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
+      <c r="C166" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>as no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-018</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr"/>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>. | VIU 2026-07-22 LIVE: part-row ⋮ menu = 'Move', 'Add Part Fee / Discount' (label correct; opens part fee/discount dialog). 'Return' state-gated — the seeded part was 'Auth To Order' (not received) so Return was not offered; Return appears only for returnable parts. Ev: wo/FD-WO-018-part-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-021</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr"/>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>s a mockup. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: Work Order Fees &amp; Discounts card shows disclaimer exactly 'Applies to the whole work order, after all other fees &amp; discounts.' below the adjustment list. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-025</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr"/>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>6-07-22 LIVE: toolbar ⋯ menu label 'Add Work Order Fee / Discount' correct; opens whole-WO fee/discount dialog. WORDING CORRECTED — observed order is 'Audit Log' -&gt; 'Timesheets (N)' -&gt; 'Add Work Order Fee / Discount' -&gt; 'Delete Work Order' (Add is 3rd, NOT at top). Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-028</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr"/>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Verify the tax-jurisdiction note and the 'Pass convenience fee to customer' banner still appear after the fee/discount UI updates</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>&amp; Discounts Settings page (Settings -&gt; Service -&gt; Fees &amp; Discounts / adjustment-templates) — it is NOT rendered inside the WO fee/discount dialogs. Ev: wo/labor-dialog-text.txt, wo/part-dialog-text.txt, wo/wo-dialog-text.txt, wo/FD-WO-028-settings-convenience-banner.png, wo/settings-fd-bodytext.txt.</t>
         </is>
       </c>
     </row>
@@ -7126,144 +7733,144 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7275,7 +7882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7368,7 +7975,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
     </row>
@@ -7501,32 +8108,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-002</t>
+          <t>FD-LABOR-003</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>C28441</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify the labor fee/discount add entry point is a three-dot menu to the left of the first technician (or 'Unassigned')</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7536,34 +8143,34 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
+          <t>not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: rescoped from the old per-line-row ⋮ model to the new ⋮-left-of-technician entry point + 'Add Labor Fee / Discount' (item 1). RETIRE-CANDIDATE: now overlaps kept new case FD-WO-017 (item-1 placement acceptance) — flag for user ruling. | VIU 2026-07-22 LIVE: DEVIATION — three-dot (⋮) renders to the RIGHT of 'Unassigned' (⋮ x=502 vs Unassigned right-edge x=497), but EXP/spec requires LEFT (same defect as FD-WO-017 item-#1 re-open). Label 'Add Labor Fee / Discount' correct. Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-008</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28526</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7578,34 +8185,34 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-009</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7620,34 +8227,34 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-001</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28459</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7662,7 +8269,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
         </is>
       </c>
     </row>
@@ -7788,7 +8395,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged).</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
@@ -7815,7 +8422,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
+          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7830,7 +8437,45 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged.</t>
+          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-017</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Labor-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>me row y=282); spec requires LEFT. Label 'Add Labor Fee / Discount' is correct and opens the labor fee/discount dialog. Menu contained only 'Add Labor Fee / Discount' (no separate 'Edit labor' item observed). Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png, wo/FD-WO-017-labor-menu-open.png, obs2 geometry.</t>
         </is>
       </c>
     </row>
@@ -7925,7 +8570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8025,32 +8670,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FD-FLAG-001</t>
+          <t>FD-CALC-023</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>C28596</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28596</t>
-        </is>
-      </c>
+          <t>(pending-create)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Feature-flag gating</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
+          <t>Verify that when the Fees &amp; Discounts feature is turned off, the line total is Labor + Parts only (gross), with no fee/discount rolled in</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -8060,24 +8701,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>org flag toggling deliberately NOT done: shared env, manual tester active today | WORDING+VIU 2026-07-13: BLOCKED-ENV: cannot take a feature-off window on the shared qb env while a manual tester is active. Wording made layman. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>re flag is ON at the org level on the SHARED staging org (d55bc308); toggling it OFF org-wide during an unattended run would strip F&amp;D from all users and break concurrent/later VIU batches, and no separate flag-off org is available. Not inferred — needs a dedicated flag-off org/state to verify live.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FD-FLAG-002</t>
+          <t>FD-FLAG-001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>C28597</t>
+          <t>C28596</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28596</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8087,12 +8728,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
+          <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8102,24 +8743,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV + V1_2 re-VIU pending: needs a feature-off window (not takeable on the shared env) to confirm history entries stay visible. Wording made layman. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>org flag toggling deliberately NOT done: shared env, manual tester active today | WORDING+VIU 2026-07-13: BLOCKED-ENV: cannot take a feature-off window on the shared qb env while a manual tester is active. Wording made layman. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FD-FLAG-003</t>
+          <t>FD-FLAG-002</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>C28598</t>
+          <t>C28597</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -8129,7 +8770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
+          <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8144,39 +8785,39 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>as FD-FLAG-001; the flag-ON half of the AND-gate is fresh-proven (FD-PERM-010) | WORDING+VIU 2026-07-13: BLOCKED-ENV (permission half): the See-Financial-Data masking half is established, but the full both-gates check needs a restricted-role login — re-run after the roles matrix is re-derived. Wording made layman.</t>
+          <t>as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV + V1_2 re-VIU pending: needs a feature-off window (not takeable on the shared env) to confirm history entries stay visible. Wording made layman. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-004</t>
+          <t>FD-FLAG-003</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28563</t>
+          <t>C28598</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Audit log — visibility</t>
+          <t>Feature-flag gating</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
+          <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8186,34 +8827,34 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV: needs a feature-off window (not takeable on the shared env with a live tester). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>as FD-FLAG-001; the flag-ON half of the AND-gate is fresh-proven (FD-PERM-010) | WORDING+VIU 2026-07-13: BLOCKED-ENV (permission half): the See-Financial-Data masking half is established, but the full both-gates check needs a restricted-role login — re-run after the roles matrix is re-derived. Wording made layman.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-001</t>
+          <t>FD-HIST-004</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28544</t>
+          <t>C28563</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
+          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -8228,24 +8869,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>QB invoice line internals unobservable (no read API; export of re-invoiced WOs fails on duplicate doc numbers) — needs QB-UI eyeball of a cleanly synced invoice | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+          <t>feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV: needs a feature-off window (not takeable on the shared env with a live tester). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-002</t>
+          <t>FD-QB-001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28545</t>
+          <t>C28544</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -8255,7 +8896,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
+          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -8270,39 +8911,39 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-001 — needs QB UI (generic Fee/Discount item + description=name) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+          <t>QB invoice line internals unobservable (no read API; export of re-invoiced WOs fails on duplicate doc numbers) — needs QB-UI eyeball of a cleanly synced invoice | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-003</t>
+          <t>FD-QB-002</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28546</t>
+          <t>C28545</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync — edge</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
+          <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8312,39 +8953,39 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-001 — $0-line skip only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+          <t>as FD-QB-001 — needs QB UI (generic Fee/Discount item + description=name) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-004</t>
+          <t>FD-QB-003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28547</t>
+          <t>C28546</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard</t>
+          <t>QuickBooks sync — edge</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
+          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8354,24 +8995,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>unmap not achievable today: PUT bookkeeping/settings {settings:{feeItemId:null}} -&gt; 500 (requestId 4bd14847); flat payload -&gt; 400 'settings missing'. Mapping stayed connected+mapped (verified). Guard cycle needs a working unmap (dev/QB-side) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
+          <t>as FD-QB-001 — $0-line skip only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-005</t>
+          <t>FD-QB-004</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28548</t>
+          <t>C28547</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -8381,7 +9022,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
+          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8396,39 +9037,39 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
+          <t>unmap not achievable today: PUT bookkeeping/settings {settings:{feeItemId:null}} -&gt; 500 (requestId 4bd14847); flat payload -&gt; 400 'settings missing'. Mapping stayed connected+mapped (verified). Guard cycle needs a working unmap (dev/QB-side) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-006</t>
+          <t>FD-QB-005</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C28549</t>
+          <t>C28548</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard scope</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
+          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8445,27 +9086,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-007</t>
+          <t>FD-QB-006</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C28550</t>
+          <t>C28549</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard (auto-apply)</t>
+          <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
+          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8487,27 +9128,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-008</t>
+          <t>FD-QB-007</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28551</t>
+          <t>C28550</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard exceptions</t>
+          <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
+          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8522,34 +9163,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>as FD-QB-004; positive half (template create while MAPPED) works throughout | WORDING+VIU 2026-07-13: Observable half CONFIRMED live: creating a non-auto-apply template is always allowed (template create 201). The 'no block when QuickBooks not connected' half is Blocked-Env — QuickBooks is connected here and cannot be disconnected on the shared env.</t>
+          <t>as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-009</t>
+          <t>FD-QB-008</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28552</t>
+          <t>C28551</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — unmap recovery</t>
+          <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
+          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8564,39 +9205,39 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>unexported-items list + retry + mark-done endpoints re-exercised (mark-done 200 on my entries); the unmap-in-flight repro blocked by the unmap 500 | WORDING+VIU 2026-07-13:  BLOCKED-ENV: cannot unmap an in-use item — the unmap call 500s on this env — so the route-to-Unexported-Items behavior can't be driven. (The Unexported Items list itself is reachable and returns data.)</t>
+          <t>as FD-QB-004; positive half (template create while MAPPED) works throughout | WORDING+VIU 2026-07-13: Observable half CONFIRMED live: creating a non-auto-apply template is always allowed (template create 201). The 'no block when QuickBooks not connected' half is Blocked-Env — QuickBooks is connected here and cannot be disconnected on the shared env.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-010</t>
+          <t>FD-QB-009</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28553</t>
+          <t>C28552</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class</t>
+          <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
+          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8606,34 +9247,34 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Class application only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+          <t>unexported-items list + retry + mark-done endpoints re-exercised (mark-done 200 on my entries); the unmap-in-flight repro blocked by the unmap 500 | WORDING+VIU 2026-07-13:  BLOCKED-ENV: cannot unmap an in-use item — the unmap call 500s on this env — so the route-to-Unexported-Items behavior can't be driven. (The Unexported Items list itself is reachable and returns data.)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-011</t>
+          <t>FD-QB-010</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C28554</t>
+          <t>C28553</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class validation</t>
+          <t>QuickBooks — Class</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
+          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8648,39 +9289,39 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>stale-Class abort only reproducible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+          <t>Class application only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-013</t>
+          <t>FD-QB-011</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C28556</t>
+          <t>C28554</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>QuickBooks — Class validation</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
+          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8690,24 +9331,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>penny-cap allocation of discount LINES only visible on QB invoice lines | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the largest-remainder penny allocation on the QuickBooks discount lines is only visible inside QuickBooks (same as FD-CALC-017). The in-app $0.00 floor half is verified.</t>
+          <t>stale-Class abort only reproducible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-015</t>
+          <t>FD-QB-013</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C28558</t>
+          <t>C28556</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -8717,7 +9358,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
+          <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -8732,34 +9373,34 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>IN-APP HALF VERIFIED TODAY: invoicing the over-discounted WO recorded a CUSTOMER CREDIT (unpaid-transactions 2-&gt;4; 'current' bucket -11.63 -&gt; -119.73 = +9.14 invoice &amp; -117.24 credit exactly). QB goodwill-memo half unobservable: invoice export fails on the duplicate-doc-number env bug, no credit_memo export fired, no QB read API — needs QB UI on a cleanly synced org | WORDING+VIU 2026-07-13: In-app customer-credit half VERIFIED 2026-07-10 (invoicing an over-discounted WO recorded a customer credit of exactly the excess). BLOCKED-ENV: the QuickBooks tax-exempt goodwill credit-memo half needs a human in QuickBooks (export fails on duplicate document numbers; no QB read API).</t>
+          <t>penny-cap allocation of discount LINES only visible on QB invoice lines | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the largest-remainder penny allocation on the QuickBooks discount lines is only visible inside QuickBooks (same as FD-CALC-017). The in-app $0.00 floor half is verified.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-016</t>
+          <t>FD-QB-015</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C28559</t>
+          <t>C28558</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync — tax</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
+          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8774,74 +9415,116 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>tax code on the QB line unobservable in-app; in-app taxable base shifts re-proven (FD-CALC-011) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+          <t>IN-APP HALF VERIFIED TODAY: invoicing the over-discounted WO recorded a CUSTOMER CREDIT (unpaid-transactions 2-&gt;4; 'current' bucket -11.63 -&gt; -119.73 = +9.14 invoice &amp; -117.24 credit exactly). QB goodwill-memo half unobservable: invoice export fails on the duplicate-doc-number env bug, no credit_memo export fired, no QB read API — needs QB UI on a cleanly synced org | WORDING+VIU 2026-07-13: In-app customer-credit half VERIFIED 2026-07-10 (invoicing an over-discounted WO recorded a customer credit of exactly the excess). BLOCKED-ENV: the QuickBooks tax-exempt goodwill credit-memo half needs a human in QuickBooks (export fails on duplicate document numbers; no QB read API).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>FD-QB-016</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>C28559</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks sync — tax</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>tax code on the QB line unobservable in-app; in-app taxable base shifts re-proven (FD-CALC-011) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>FD-TMPL-012</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>C28513</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct rout